--- a/data.xlsx
+++ b/data.xlsx
@@ -71,7 +71,7 @@
     <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="180" formatCode="[$-404]e&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1211,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1"/>
@@ -3157,6 +3157,9 @@
       <c r="E60" s="1">
         <v>19</v>
       </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
@@ -3174,8 +3177,1238 @@
       <c r="A61" s="2">
         <v>46020</v>
       </c>
+      <c r="B61" s="1">
+        <v>4063</v>
+      </c>
+      <c r="C61" s="1">
+        <v>3776</v>
+      </c>
       <c r="D61" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D61:D92" si="3">B61-C61</f>
+        <v>287</v>
+      </c>
+      <c r="E61" s="1">
+        <v>75</v>
+      </c>
+      <c r="F61" s="1">
+        <v>5</v>
+      </c>
+      <c r="G61" s="1">
+        <v>7</v>
+      </c>
+      <c r="H61" s="1">
+        <v>210</v>
+      </c>
+      <c r="I61" s="1">
+        <v>4</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:10">
+      <c r="A62" s="2">
+        <v>46021</v>
+      </c>
+      <c r="B62" s="1">
+        <v>4045</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3715</v>
+      </c>
+      <c r="D62" s="1">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
+      <c r="E62" s="1">
+        <v>67</v>
+      </c>
+      <c r="F62" s="1">
+        <v>10</v>
+      </c>
+      <c r="G62" s="1">
+        <v>9</v>
+      </c>
+      <c r="H62" s="1">
+        <v>215</v>
+      </c>
+      <c r="I62" s="1">
+        <v>6</v>
+      </c>
+      <c r="J62" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:10">
+      <c r="A63" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B63" s="1">
+        <v>4675</v>
+      </c>
+      <c r="C63" s="1">
+        <v>4328</v>
+      </c>
+      <c r="D63" s="1">
+        <f t="shared" si="3"/>
+        <v>347</v>
+      </c>
+      <c r="E63" s="1">
+        <v>90</v>
+      </c>
+      <c r="F63" s="1">
+        <v>4</v>
+      </c>
+      <c r="G63" s="1">
+        <v>4</v>
+      </c>
+      <c r="H63" s="1">
+        <v>215</v>
+      </c>
+      <c r="I63" s="1">
+        <v>8</v>
+      </c>
+      <c r="J63" s="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:10">
+      <c r="A64" s="2">
+        <v>46023</v>
+      </c>
+      <c r="B64" s="1">
+        <v>287</v>
+      </c>
+      <c r="C64" s="1">
+        <v>166</v>
+      </c>
+      <c r="D64" s="1">
+        <f t="shared" si="3"/>
+        <v>121</v>
+      </c>
+      <c r="E64" s="1">
+        <v>5</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>16</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:10">
+      <c r="A65" s="2">
+        <v>46024</v>
+      </c>
+      <c r="B65" s="1">
+        <v>2516</v>
+      </c>
+      <c r="C65" s="1">
+        <v>2300</v>
+      </c>
+      <c r="D65" s="1">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+      <c r="E65" s="1">
+        <v>54</v>
+      </c>
+      <c r="F65" s="1">
+        <v>3</v>
+      </c>
+      <c r="G65" s="1">
+        <v>3</v>
+      </c>
+      <c r="H65" s="1">
+        <v>192</v>
+      </c>
+      <c r="I65" s="1">
+        <v>2</v>
+      </c>
+      <c r="J65" s="1">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:10">
+      <c r="A66" s="2">
+        <v>46025</v>
+      </c>
+      <c r="B66" s="1">
+        <v>3586</v>
+      </c>
+      <c r="C66" s="1">
+        <v>3299</v>
+      </c>
+      <c r="D66" s="1">
+        <f t="shared" si="3"/>
+        <v>287</v>
+      </c>
+      <c r="E66" s="1">
+        <v>78</v>
+      </c>
+      <c r="F66" s="1">
+        <v>3</v>
+      </c>
+      <c r="G66" s="1">
+        <v>3</v>
+      </c>
+      <c r="H66" s="1">
+        <v>207</v>
+      </c>
+      <c r="I66" s="1">
+        <v>5</v>
+      </c>
+      <c r="J66" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:10">
+      <c r="A67" s="2">
+        <v>46026</v>
+      </c>
+      <c r="B67" s="1">
+        <v>632</v>
+      </c>
+      <c r="C67" s="1">
+        <v>188</v>
+      </c>
+      <c r="D67" s="1">
+        <f t="shared" si="3"/>
+        <v>444</v>
+      </c>
+      <c r="E67" s="1">
+        <v>21</v>
+      </c>
+      <c r="F67" s="1">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2</v>
+      </c>
+      <c r="H67" s="1">
+        <v>16</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:10">
+      <c r="A68" s="2">
+        <v>46027</v>
+      </c>
+      <c r="B68" s="1">
+        <v>4199</v>
+      </c>
+      <c r="C68" s="1">
+        <v>3771</v>
+      </c>
+      <c r="D68" s="1">
+        <f t="shared" si="3"/>
+        <v>428</v>
+      </c>
+      <c r="E68" s="1">
+        <v>107</v>
+      </c>
+      <c r="F68" s="1">
+        <v>11</v>
+      </c>
+      <c r="G68" s="1">
+        <v>14</v>
+      </c>
+      <c r="H68" s="1">
+        <v>214</v>
+      </c>
+      <c r="I68" s="1">
+        <v>18</v>
+      </c>
+      <c r="J68" s="1">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:10">
+      <c r="A69" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B69" s="1">
+        <v>3126</v>
+      </c>
+      <c r="C69" s="1">
+        <v>2745</v>
+      </c>
+      <c r="D69" s="1">
+        <f t="shared" si="3"/>
+        <v>381</v>
+      </c>
+      <c r="E69" s="1">
+        <v>89</v>
+      </c>
+      <c r="F69" s="1">
+        <v>7</v>
+      </c>
+      <c r="G69" s="1">
+        <v>8</v>
+      </c>
+      <c r="H69" s="1">
+        <v>235</v>
+      </c>
+      <c r="I69" s="1">
+        <v>8</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:10">
+      <c r="A70" s="2">
+        <v>46029</v>
+      </c>
+      <c r="B70" s="1">
+        <v>4371</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3925</v>
+      </c>
+      <c r="D70" s="1">
+        <f t="shared" si="3"/>
+        <v>446</v>
+      </c>
+      <c r="E70" s="1">
+        <v>77</v>
+      </c>
+      <c r="F70" s="1">
+        <v>7</v>
+      </c>
+      <c r="G70" s="1">
+        <v>7</v>
+      </c>
+      <c r="H70" s="1">
+        <v>216</v>
+      </c>
+      <c r="I70" s="1">
+        <v>13</v>
+      </c>
+      <c r="J70" s="1">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:10">
+      <c r="A71" s="2">
+        <v>46030</v>
+      </c>
+      <c r="B71" s="1">
+        <v>5113</v>
+      </c>
+      <c r="C71" s="1">
+        <v>4730</v>
+      </c>
+      <c r="D71" s="1">
+        <f t="shared" si="3"/>
+        <v>383</v>
+      </c>
+      <c r="E71" s="1">
+        <v>81</v>
+      </c>
+      <c r="F71" s="1">
+        <v>2</v>
+      </c>
+      <c r="G71" s="1">
+        <v>3</v>
+      </c>
+      <c r="H71" s="1">
+        <v>220</v>
+      </c>
+      <c r="I71" s="1">
+        <v>4</v>
+      </c>
+      <c r="J71" s="1">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:10">
+      <c r="A72" s="2">
+        <v>46031</v>
+      </c>
+      <c r="B72" s="1">
+        <v>4524</v>
+      </c>
+      <c r="C72" s="1">
+        <v>4257</v>
+      </c>
+      <c r="D72" s="1">
+        <f t="shared" si="3"/>
+        <v>267</v>
+      </c>
+      <c r="E72" s="1">
+        <v>72</v>
+      </c>
+      <c r="G72" s="1">
+        <v>6</v>
+      </c>
+      <c r="H72" s="1">
+        <v>229</v>
+      </c>
+      <c r="I72" s="1">
+        <v>3</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:10">
+      <c r="A73" s="2">
+        <v>46032</v>
+      </c>
+      <c r="D73" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:10">
+      <c r="A74" s="2">
+        <v>46033</v>
+      </c>
+      <c r="D74" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:10">
+      <c r="A75" s="2">
+        <v>46034</v>
+      </c>
+      <c r="D75" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:10">
+      <c r="A76" s="2">
+        <v>46035</v>
+      </c>
+      <c r="D76" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:10">
+      <c r="A77" s="2">
+        <v>46036</v>
+      </c>
+      <c r="D77" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:10">
+      <c r="A78" s="2">
+        <v>46037</v>
+      </c>
+      <c r="D78" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:10">
+      <c r="A79" s="2">
+        <v>46038</v>
+      </c>
+      <c r="D79" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:10">
+      <c r="A80" s="2">
+        <v>46039</v>
+      </c>
+      <c r="D80" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:4">
+      <c r="A81" s="2">
+        <v>46040</v>
+      </c>
+      <c r="D81" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:4">
+      <c r="A82" s="2">
+        <v>46041</v>
+      </c>
+      <c r="D82" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:4">
+      <c r="A83" s="2">
+        <v>46042</v>
+      </c>
+      <c r="D83" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:4">
+      <c r="A84" s="2">
+        <v>46043</v>
+      </c>
+      <c r="D84" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:4">
+      <c r="A85" s="2">
+        <v>46044</v>
+      </c>
+      <c r="D85" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:4">
+      <c r="A86" s="2">
+        <v>46045</v>
+      </c>
+      <c r="D86" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:4">
+      <c r="A87" s="2">
+        <v>46046</v>
+      </c>
+      <c r="D87" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:4">
+      <c r="A88" s="2">
+        <v>46047</v>
+      </c>
+      <c r="D88" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:4">
+      <c r="A89" s="2">
+        <v>46048</v>
+      </c>
+      <c r="D89" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:4">
+      <c r="A90" s="2">
+        <v>46049</v>
+      </c>
+      <c r="D90" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:4">
+      <c r="A91" s="2">
+        <v>46050</v>
+      </c>
+      <c r="D91" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:4">
+      <c r="A92" s="2">
+        <v>46051</v>
+      </c>
+      <c r="D92" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:4">
+      <c r="A93" s="2">
+        <v>46052</v>
+      </c>
+      <c r="D93" s="1">
+        <f t="shared" ref="D93:D124" si="4">B93-C93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:4">
+      <c r="A94" s="2">
+        <v>46053</v>
+      </c>
+      <c r="D94" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:4">
+      <c r="A95" s="2">
+        <v>46054</v>
+      </c>
+      <c r="D95" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:4">
+      <c r="A96" s="2">
+        <v>46055</v>
+      </c>
+      <c r="D96" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:4">
+      <c r="A97" s="2">
+        <v>46056</v>
+      </c>
+      <c r="D97" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:4">
+      <c r="A98" s="2">
+        <v>46057</v>
+      </c>
+      <c r="D98" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:4">
+      <c r="A99" s="2">
+        <v>46058</v>
+      </c>
+      <c r="D99" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:4">
+      <c r="A100" s="2">
+        <v>46059</v>
+      </c>
+      <c r="D100" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:4">
+      <c r="A101" s="2">
+        <v>46060</v>
+      </c>
+      <c r="D101" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:4">
+      <c r="A102" s="2">
+        <v>46061</v>
+      </c>
+      <c r="D102" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:4">
+      <c r="A103" s="2">
+        <v>46062</v>
+      </c>
+      <c r="D103" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="1:4">
+      <c r="A104" s="2">
+        <v>46063</v>
+      </c>
+      <c r="D104" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:4">
+      <c r="A105" s="2">
+        <v>46064</v>
+      </c>
+      <c r="D105" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:4">
+      <c r="A106" s="2">
+        <v>46065</v>
+      </c>
+      <c r="D106" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="1:4">
+      <c r="A107" s="2">
+        <v>46066</v>
+      </c>
+      <c r="D107" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="1:4">
+      <c r="A108" s="2">
+        <v>46067</v>
+      </c>
+      <c r="D108" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="1:4">
+      <c r="A109" s="2">
+        <v>46068</v>
+      </c>
+      <c r="D109" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="1:4">
+      <c r="A110" s="2">
+        <v>46069</v>
+      </c>
+      <c r="D110" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:4">
+      <c r="A111" s="2">
+        <v>46070</v>
+      </c>
+      <c r="D111" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="1:4">
+      <c r="A112" s="2">
+        <v>46071</v>
+      </c>
+      <c r="D112" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:4">
+      <c r="A113" s="2">
+        <v>46072</v>
+      </c>
+      <c r="D113" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="1:4">
+      <c r="A114" s="2">
+        <v>46073</v>
+      </c>
+      <c r="D114" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="1:4">
+      <c r="A115" s="2">
+        <v>46074</v>
+      </c>
+      <c r="D115" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="1:4">
+      <c r="A116" s="2">
+        <v>46075</v>
+      </c>
+      <c r="D116" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="1:4">
+      <c r="A117" s="2">
+        <v>46076</v>
+      </c>
+      <c r="D117" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="1:4">
+      <c r="A118" s="2">
+        <v>46077</v>
+      </c>
+      <c r="D118" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="1:4">
+      <c r="A119" s="2">
+        <v>46078</v>
+      </c>
+      <c r="D119" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="1:4">
+      <c r="A120" s="2">
+        <v>46079</v>
+      </c>
+      <c r="D120" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="1:4">
+      <c r="A121" s="2">
+        <v>46080</v>
+      </c>
+      <c r="D121" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="1:4">
+      <c r="A122" s="2">
+        <v>46081</v>
+      </c>
+      <c r="D122" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="1:4">
+      <c r="A123" s="2">
+        <v>46082</v>
+      </c>
+      <c r="D123" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="1:4">
+      <c r="A124" s="2">
+        <v>46083</v>
+      </c>
+      <c r="D124" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="1:4">
+      <c r="A125" s="2">
+        <v>46084</v>
+      </c>
+      <c r="D125" s="1">
+        <f>B125-C125</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="1:4">
+      <c r="A126" s="2">
+        <v>46085</v>
+      </c>
+      <c r="D126" s="1">
+        <f>B126-C126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:4">
+      <c r="A127" s="2">
+        <v>46086</v>
+      </c>
+      <c r="D127" s="1">
+        <f>B127-C127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:4">
+      <c r="A128" s="2">
+        <v>46087</v>
+      </c>
+      <c r="D128" s="1">
+        <f>B128-C128</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="1:4">
+      <c r="A129" s="2">
+        <v>46088</v>
+      </c>
+      <c r="D129" s="1">
+        <f>B129-C129</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="1:4">
+      <c r="A130" s="2">
+        <v>46089</v>
+      </c>
+      <c r="D130" s="1">
+        <f t="shared" ref="D130:D166" si="5">B130-C130</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="1:4">
+      <c r="A131" s="2">
+        <v>46090</v>
+      </c>
+      <c r="D131" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="1:4">
+      <c r="A132" s="2">
+        <v>46091</v>
+      </c>
+      <c r="D132" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="1:4">
+      <c r="A133" s="2">
+        <v>46092</v>
+      </c>
+      <c r="D133" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="1:4">
+      <c r="A134" s="2">
+        <v>46093</v>
+      </c>
+      <c r="D134" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="1:4">
+      <c r="A135" s="2">
+        <v>46094</v>
+      </c>
+      <c r="D135" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="1:4">
+      <c r="A136" s="2">
+        <v>46095</v>
+      </c>
+      <c r="D136" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="1:4">
+      <c r="A137" s="2">
+        <v>46096</v>
+      </c>
+      <c r="D137" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="1:4">
+      <c r="A138" s="2">
+        <v>46097</v>
+      </c>
+      <c r="D138" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="1:4">
+      <c r="A139" s="2">
+        <v>46098</v>
+      </c>
+      <c r="D139" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="1:4">
+      <c r="A140" s="2">
+        <v>46099</v>
+      </c>
+      <c r="D140" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="1:4">
+      <c r="A141" s="2">
+        <v>46100</v>
+      </c>
+      <c r="D141" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="1:4">
+      <c r="A142" s="2">
+        <v>46101</v>
+      </c>
+      <c r="D142" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="1:4">
+      <c r="A143" s="2">
+        <v>46102</v>
+      </c>
+      <c r="D143" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:4">
+      <c r="A144" s="2">
+        <v>46103</v>
+      </c>
+      <c r="D144" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="1:4">
+      <c r="A145" s="2">
+        <v>46104</v>
+      </c>
+      <c r="D145" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="1:4">
+      <c r="A146" s="2">
+        <v>46105</v>
+      </c>
+      <c r="D146" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="1:4">
+      <c r="A147" s="2">
+        <v>46106</v>
+      </c>
+      <c r="D147" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="1:4">
+      <c r="A148" s="2">
+        <v>46107</v>
+      </c>
+      <c r="D148" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="1:4">
+      <c r="A149" s="2">
+        <v>46108</v>
+      </c>
+      <c r="D149" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="1:4">
+      <c r="A150" s="2">
+        <v>46109</v>
+      </c>
+      <c r="D150" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="1:4">
+      <c r="A151" s="2">
+        <v>46110</v>
+      </c>
+      <c r="D151" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="1:4">
+      <c r="A152" s="2">
+        <v>46111</v>
+      </c>
+      <c r="D152" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="1:4">
+      <c r="A153" s="2">
+        <v>46112</v>
+      </c>
+      <c r="D153" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="1:4">
+      <c r="A154" s="2">
+        <v>46113</v>
+      </c>
+      <c r="D154" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="1:4">
+      <c r="A155" s="2">
+        <v>46114</v>
+      </c>
+      <c r="D155" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="1:4">
+      <c r="A156" s="2">
+        <v>46115</v>
+      </c>
+      <c r="D156" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="1:4">
+      <c r="A157" s="2">
+        <v>46116</v>
+      </c>
+      <c r="D157" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="1:4">
+      <c r="A158" s="2">
+        <v>46117</v>
+      </c>
+      <c r="D158" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="1:4">
+      <c r="A159" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D159" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="1:4">
+      <c r="A160" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D160" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="1:4">
+      <c r="A161" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D161" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="1:4">
+      <c r="A162" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D162" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="1:4">
+      <c r="A163" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D163" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="1:4">
+      <c r="A164" s="2">
+        <v>46123</v>
+      </c>
+      <c r="D164" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="1:4">
+      <c r="A165" s="2">
+        <v>46124</v>
+      </c>
+      <c r="D165" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="1:4">
+      <c r="A166" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D166" s="1">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3553,6 +3553,9 @@
       <c r="E72" s="1">
         <v>72</v>
       </c>
+      <c r="F72" s="1">
+        <v>5</v>
+      </c>
       <c r="G72" s="1">
         <v>6</v>
       </c>
@@ -3570,63 +3573,231 @@
       <c r="A73" s="2">
         <v>46032</v>
       </c>
+      <c r="B73" s="1">
+        <v>2476</v>
+      </c>
+      <c r="C73" s="1">
+        <v>2152</v>
+      </c>
       <c r="D73" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>324</v>
+      </c>
+      <c r="E73" s="1">
+        <v>49</v>
+      </c>
+      <c r="F73" s="1">
+        <v>2</v>
+      </c>
+      <c r="G73" s="1">
+        <v>2</v>
+      </c>
+      <c r="H73" s="1">
+        <v>87</v>
+      </c>
+      <c r="I73" s="1">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <v>607</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:10">
       <c r="A74" s="2">
         <v>46033</v>
       </c>
+      <c r="B74" s="1">
+        <v>419</v>
+      </c>
+      <c r="C74" s="1">
+        <v>99</v>
+      </c>
       <c r="D74" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>320</v>
+      </c>
+      <c r="E74" s="1">
+        <v>11</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1">
+        <v>16</v>
+      </c>
+      <c r="I74" s="1">
+        <v>1</v>
+      </c>
+      <c r="J74" s="1">
+        <v>711</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:10">
       <c r="A75" s="2">
         <v>46034</v>
       </c>
+      <c r="B75" s="1">
+        <v>3828</v>
+      </c>
+      <c r="C75" s="1">
+        <v>3495</v>
+      </c>
       <c r="D75" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>333</v>
+      </c>
+      <c r="E75" s="1">
+        <v>86</v>
+      </c>
+      <c r="F75" s="1">
+        <v>3</v>
+      </c>
+      <c r="G75" s="1">
+        <v>4</v>
+      </c>
+      <c r="H75" s="1">
+        <v>165</v>
+      </c>
+      <c r="I75" s="1">
+        <v>10</v>
+      </c>
+      <c r="J75" s="1">
+        <v>2399</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:10">
       <c r="A76" s="2">
         <v>46035</v>
       </c>
+      <c r="B76" s="1">
+        <v>4322</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3899</v>
+      </c>
       <c r="D76" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>423</v>
+      </c>
+      <c r="E76" s="1">
+        <v>94</v>
+      </c>
+      <c r="F76" s="1">
+        <v>9</v>
+      </c>
+      <c r="G76" s="1">
+        <v>10</v>
+      </c>
+      <c r="H76" s="1">
+        <v>245</v>
+      </c>
+      <c r="I76" s="1">
+        <v>3</v>
+      </c>
+      <c r="J76" s="1">
+        <v>952</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:10">
       <c r="A77" s="2">
         <v>46036</v>
       </c>
+      <c r="B77" s="1">
+        <v>5182</v>
+      </c>
+      <c r="C77" s="1">
+        <v>4718</v>
+      </c>
       <c r="D77" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>464</v>
+      </c>
+      <c r="E77" s="1">
+        <v>97</v>
+      </c>
+      <c r="F77" s="1">
+        <v>6</v>
+      </c>
+      <c r="G77" s="1">
+        <v>8</v>
+      </c>
+      <c r="H77" s="1">
+        <v>253</v>
+      </c>
+      <c r="I77" s="1">
+        <v>5</v>
+      </c>
+      <c r="J77" s="1">
+        <v>578</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:10">
       <c r="A78" s="2">
         <v>46037</v>
       </c>
+      <c r="B78" s="1">
+        <v>3761</v>
+      </c>
+      <c r="C78" s="1">
+        <v>3360</v>
+      </c>
       <c r="D78" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>401</v>
+      </c>
+      <c r="E78" s="1">
+        <v>100</v>
+      </c>
+      <c r="F78" s="1">
+        <v>6</v>
+      </c>
+      <c r="G78" s="1">
+        <v>7</v>
+      </c>
+      <c r="H78" s="1">
+        <v>232</v>
+      </c>
+      <c r="I78" s="1">
+        <v>13</v>
+      </c>
+      <c r="J78" s="1">
+        <v>3132</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:10">
       <c r="A79" s="2">
         <v>46038</v>
       </c>
+      <c r="B79" s="1">
+        <v>4449</v>
+      </c>
+      <c r="C79" s="1">
+        <v>3986</v>
+      </c>
       <c r="D79" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>463</v>
+      </c>
+      <c r="E79" s="1">
+        <v>111</v>
+      </c>
+      <c r="F79" s="1">
+        <v>11</v>
+      </c>
+      <c r="G79" s="1">
+        <v>12</v>
+      </c>
+      <c r="H79" s="1">
+        <v>235</v>
+      </c>
+      <c r="I79" s="1">
+        <v>8</v>
+      </c>
+      <c r="J79" s="1">
+        <v>7984</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:10">
@@ -3751,7 +3922,7 @@
         <v>46052</v>
       </c>
       <c r="D93" s="1">
-        <f t="shared" ref="D93:D124" si="4">B93-C93</f>
+        <f t="shared" ref="D93:D129" si="4">B93-C93</f>
         <v>0</v>
       </c>
     </row>
@@ -4039,7 +4210,7 @@
         <v>46084</v>
       </c>
       <c r="D125" s="1">
-        <f>B125-C125</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -4048,7 +4219,7 @@
         <v>46085</v>
       </c>
       <c r="D126" s="1">
-        <f>B126-C126</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -4057,7 +4228,7 @@
         <v>46086</v>
       </c>
       <c r="D127" s="1">
-        <f>B127-C127</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -4066,7 +4237,7 @@
         <v>46087</v>
       </c>
       <c r="D128" s="1">
-        <f>B128-C128</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -4075,7 +4246,7 @@
         <v>46088</v>
       </c>
       <c r="D129" s="1">
-        <f>B129-C129</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3804,66 +3804,234 @@
       <c r="A80" s="2">
         <v>46039</v>
       </c>
+      <c r="B80" s="1">
+        <v>4197</v>
+      </c>
+      <c r="C80" s="1">
+        <v>3747</v>
+      </c>
       <c r="D80" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="1:4">
+        <v>450</v>
+      </c>
+      <c r="E80" s="1">
+        <v>76</v>
+      </c>
+      <c r="F80" s="1">
+        <v>7</v>
+      </c>
+      <c r="G80" s="1">
+        <v>8</v>
+      </c>
+      <c r="H80" s="1">
+        <v>227</v>
+      </c>
+      <c r="I80" s="1">
+        <v>10</v>
+      </c>
+      <c r="J80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:10">
       <c r="A81" s="2">
         <v>46040</v>
       </c>
+      <c r="B81" s="1">
+        <v>844</v>
+      </c>
+      <c r="C81" s="1">
+        <v>473</v>
+      </c>
       <c r="D81" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="1:4">
+        <v>371</v>
+      </c>
+      <c r="E81" s="1">
+        <v>40</v>
+      </c>
+      <c r="F81" s="1">
+        <v>2</v>
+      </c>
+      <c r="G81" s="1">
+        <v>3</v>
+      </c>
+      <c r="H81" s="1">
+        <v>76</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1</v>
+      </c>
+      <c r="J81" s="1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:10">
       <c r="A82" s="2">
         <v>46041</v>
       </c>
+      <c r="B82" s="1">
+        <v>4343</v>
+      </c>
+      <c r="C82" s="1">
+        <v>3786</v>
+      </c>
       <c r="D82" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="1:4">
+        <v>557</v>
+      </c>
+      <c r="E82" s="1">
+        <v>99</v>
+      </c>
+      <c r="F82" s="1">
+        <v>9</v>
+      </c>
+      <c r="G82" s="1">
+        <v>10</v>
+      </c>
+      <c r="H82" s="1">
+        <v>201</v>
+      </c>
+      <c r="I82" s="1">
+        <v>21</v>
+      </c>
+      <c r="J82" s="1">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:10">
       <c r="A83" s="2">
         <v>46042</v>
       </c>
+      <c r="B83" s="1">
+        <v>6079</v>
+      </c>
+      <c r="C83" s="1">
+        <v>5299</v>
+      </c>
       <c r="D83" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="1:4">
+        <v>780</v>
+      </c>
+      <c r="E83" s="1">
+        <v>104</v>
+      </c>
+      <c r="F83" s="1">
+        <v>9</v>
+      </c>
+      <c r="G83" s="1">
+        <v>10</v>
+      </c>
+      <c r="H83" s="1">
+        <v>236</v>
+      </c>
+      <c r="I83" s="1">
+        <v>12</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:10">
       <c r="A84" s="2">
         <v>46043</v>
       </c>
+      <c r="B84" s="1">
+        <v>6328</v>
+      </c>
+      <c r="C84" s="1">
+        <v>5650</v>
+      </c>
       <c r="D84" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="1:4">
+        <v>678</v>
+      </c>
+      <c r="E84" s="1">
+        <v>109</v>
+      </c>
+      <c r="F84" s="1">
+        <v>8</v>
+      </c>
+      <c r="G84" s="1">
+        <v>9</v>
+      </c>
+      <c r="H84" s="1">
+        <v>211</v>
+      </c>
+      <c r="I84" s="1">
+        <v>11</v>
+      </c>
+      <c r="J84" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:10">
       <c r="A85" s="2">
         <v>46044</v>
       </c>
+      <c r="B85" s="1">
+        <v>7261</v>
+      </c>
+      <c r="C85" s="1">
+        <v>6757</v>
+      </c>
       <c r="D85" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="1:4">
+        <v>504</v>
+      </c>
+      <c r="E85" s="1">
+        <v>102</v>
+      </c>
+      <c r="F85" s="1">
+        <v>7</v>
+      </c>
+      <c r="G85" s="1">
+        <v>8</v>
+      </c>
+      <c r="H85" s="1">
+        <v>221</v>
+      </c>
+      <c r="I85" s="1">
+        <v>9</v>
+      </c>
+      <c r="J85" s="1">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:10">
       <c r="A86" s="2">
         <v>46045</v>
       </c>
+      <c r="B86" s="1">
+        <v>6107</v>
+      </c>
+      <c r="C86" s="1">
+        <v>5561</v>
+      </c>
       <c r="D86" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="1:4">
+        <v>546</v>
+      </c>
+      <c r="E86" s="1">
+        <v>115</v>
+      </c>
+      <c r="F86" s="1">
+        <v>4</v>
+      </c>
+      <c r="G86" s="1">
+        <v>5</v>
+      </c>
+      <c r="H86" s="1">
+        <v>233</v>
+      </c>
+      <c r="I86" s="1">
+        <v>8</v>
+      </c>
+      <c r="J86" s="1">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:10">
       <c r="A87" s="2">
         <v>46046</v>
       </c>
@@ -3872,7 +4040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="1:4">
+    <row r="88" customHeight="1" spans="1:10">
       <c r="A88" s="2">
         <v>46047</v>
       </c>
@@ -3881,7 +4049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="1:4">
+    <row r="89" customHeight="1" spans="1:10">
       <c r="A89" s="2">
         <v>46048</v>
       </c>
@@ -3890,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:4">
+    <row r="90" customHeight="1" spans="1:10">
       <c r="A90" s="2">
         <v>46049</v>
       </c>
@@ -3899,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="1:4">
+    <row r="91" customHeight="1" spans="1:10">
       <c r="A91" s="2">
         <v>46050</v>
       </c>
@@ -3908,7 +4076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:4">
+    <row r="92" customHeight="1" spans="1:10">
       <c r="A92" s="2">
         <v>46051</v>
       </c>
@@ -3917,7 +4085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:4">
+    <row r="93" customHeight="1" spans="1:10">
       <c r="A93" s="2">
         <v>46052</v>
       </c>
@@ -3926,7 +4094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="1:4">
+    <row r="94" customHeight="1" spans="1:10">
       <c r="A94" s="2">
         <v>46053</v>
       </c>
@@ -3935,7 +4103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="1:4">
+    <row r="95" customHeight="1" spans="1:10">
       <c r="A95" s="2">
         <v>46054</v>
       </c>
@@ -3944,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:4">
+    <row r="96" customHeight="1" spans="1:10">
       <c r="A96" s="2">
         <v>46055</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="13545" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4035,8 +4035,32 @@
       <c r="A87" s="2">
         <v>46046</v>
       </c>
+      <c r="B87" s="1">
+        <v>5388</v>
+      </c>
+      <c r="C87" s="1">
+        <v>4991</v>
+      </c>
       <c r="D87" s="1">
         <f t="shared" si="3"/>
+        <v>397</v>
+      </c>
+      <c r="E87" s="1">
+        <v>96</v>
+      </c>
+      <c r="F87" s="1">
+        <v>3</v>
+      </c>
+      <c r="G87" s="1">
+        <v>3</v>
+      </c>
+      <c r="H87" s="1">
+        <v>158</v>
+      </c>
+      <c r="I87" s="1">
+        <v>2</v>
+      </c>
+      <c r="J87" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4044,27 +4068,99 @@
       <c r="A88" s="2">
         <v>46047</v>
       </c>
+      <c r="B88" s="1">
+        <v>417</v>
+      </c>
+      <c r="C88" s="1">
+        <v>124</v>
+      </c>
       <c r="D88" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>293</v>
+      </c>
+      <c r="E88" s="1">
+        <v>14</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
+        <v>16</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:10">
       <c r="A89" s="2">
         <v>46048</v>
       </c>
+      <c r="B89" s="1">
+        <v>5270</v>
+      </c>
+      <c r="C89" s="1">
+        <v>4798</v>
+      </c>
       <c r="D89" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>472</v>
+      </c>
+      <c r="E89" s="1">
+        <v>108</v>
+      </c>
+      <c r="F89" s="1">
+        <v>9</v>
+      </c>
+      <c r="G89" s="1">
+        <v>9</v>
+      </c>
+      <c r="H89" s="1">
+        <v>216</v>
+      </c>
+      <c r="I89" s="1">
+        <v>7</v>
+      </c>
+      <c r="J89" s="1">
+        <v>567</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:10">
       <c r="A90" s="2">
         <v>46049</v>
       </c>
+      <c r="B90" s="1">
+        <v>6930</v>
+      </c>
+      <c r="C90" s="1">
+        <v>6352</v>
+      </c>
       <c r="D90" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>578</v>
+      </c>
+      <c r="E90" s="1">
+        <v>91</v>
+      </c>
+      <c r="F90" s="1">
+        <v>5</v>
+      </c>
+      <c r="G90" s="1">
+        <v>8</v>
+      </c>
+      <c r="H90" s="1">
+        <v>224</v>
+      </c>
+      <c r="I90" s="1">
+        <v>5</v>
+      </c>
+      <c r="J90" s="1">
+        <v>13</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:10">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4167,35 +4167,131 @@
       <c r="A91" s="2">
         <v>46050</v>
       </c>
+      <c r="B91" s="1">
+        <v>7446</v>
+      </c>
+      <c r="C91" s="1">
+        <v>6624</v>
+      </c>
       <c r="D91" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>822</v>
+      </c>
+      <c r="E91" s="1">
+        <v>123</v>
+      </c>
+      <c r="F91" s="1">
+        <v>6</v>
+      </c>
+      <c r="G91" s="1">
+        <v>7</v>
+      </c>
+      <c r="H91" s="1">
+        <v>230</v>
+      </c>
+      <c r="I91" s="1">
+        <v>5</v>
+      </c>
+      <c r="J91" s="1">
+        <v>34</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:10">
       <c r="A92" s="2">
         <v>46051</v>
       </c>
+      <c r="B92" s="1">
+        <v>6656</v>
+      </c>
+      <c r="C92" s="1">
+        <v>6138</v>
+      </c>
       <c r="D92" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>518</v>
+      </c>
+      <c r="E92" s="1">
+        <v>160</v>
+      </c>
+      <c r="F92" s="1">
+        <v>6</v>
+      </c>
+      <c r="G92" s="1">
+        <v>6</v>
+      </c>
+      <c r="H92" s="1">
+        <v>233</v>
+      </c>
+      <c r="I92" s="1">
+        <v>5</v>
+      </c>
+      <c r="J92" s="1">
+        <v>874</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:10">
       <c r="A93" s="2">
         <v>46052</v>
       </c>
+      <c r="B93" s="1">
+        <v>5397</v>
+      </c>
+      <c r="C93" s="1">
+        <v>4797</v>
+      </c>
       <c r="D93" s="1">
         <f t="shared" ref="D93:D129" si="4">B93-C93</f>
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="E93" s="1">
+        <v>107</v>
+      </c>
+      <c r="F93" s="1">
+        <v>15</v>
+      </c>
+      <c r="G93" s="1">
+        <v>16</v>
+      </c>
+      <c r="H93" s="1">
+        <v>203</v>
+      </c>
+      <c r="I93" s="1">
+        <v>4</v>
+      </c>
+      <c r="J93" s="1">
+        <v>674</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="1:10">
       <c r="A94" s="2">
         <v>46053</v>
       </c>
+      <c r="B94" s="1">
+        <v>6492</v>
+      </c>
+      <c r="C94" s="1">
+        <v>5945</v>
+      </c>
       <c r="D94" s="1">
         <f t="shared" si="4"/>
+        <v>547</v>
+      </c>
+      <c r="E94" s="1">
+        <v>102</v>
+      </c>
+      <c r="F94" s="1">
+        <v>5</v>
+      </c>
+      <c r="G94" s="1">
+        <v>5</v>
+      </c>
+      <c r="H94" s="1">
+        <v>202</v>
+      </c>
+      <c r="I94" s="1">
+        <v>4</v>
+      </c>
+      <c r="J94" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4203,8 +4299,32 @@
       <c r="A95" s="2">
         <v>46054</v>
       </c>
+      <c r="B95" s="1">
+        <v>508</v>
+      </c>
+      <c r="C95" s="1">
+        <v>177</v>
+      </c>
       <c r="D95" s="1">
         <f t="shared" si="4"/>
+        <v>331</v>
+      </c>
+      <c r="E95" s="1">
+        <v>10</v>
+      </c>
+      <c r="F95" s="1">
+        <v>1</v>
+      </c>
+      <c r="G95" s="1">
+        <v>1</v>
+      </c>
+      <c r="H95" s="1">
+        <v>16</v>
+      </c>
+      <c r="I95" s="1">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4212,39 +4332,135 @@
       <c r="A96" s="2">
         <v>46055</v>
       </c>
+      <c r="B96" s="1">
+        <v>4044</v>
+      </c>
+      <c r="C96" s="1">
+        <v>3742</v>
+      </c>
       <c r="D96" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" spans="1:4">
+        <v>302</v>
+      </c>
+      <c r="E96" s="1">
+        <v>100</v>
+      </c>
+      <c r="F96" s="1">
+        <v>3</v>
+      </c>
+      <c r="G96" s="1">
+        <v>3</v>
+      </c>
+      <c r="H96" s="1">
+        <v>221</v>
+      </c>
+      <c r="I96" s="1">
+        <v>6</v>
+      </c>
+      <c r="J96" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:10">
       <c r="A97" s="2">
         <v>46056</v>
       </c>
+      <c r="B97" s="1">
+        <v>4858</v>
+      </c>
+      <c r="C97" s="1">
+        <v>4543</v>
+      </c>
       <c r="D97" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="1:4">
+        <v>315</v>
+      </c>
+      <c r="E97" s="1">
+        <v>89</v>
+      </c>
+      <c r="F97" s="1">
+        <v>5</v>
+      </c>
+      <c r="G97" s="1">
+        <v>5</v>
+      </c>
+      <c r="H97" s="1">
+        <v>203</v>
+      </c>
+      <c r="I97" s="1">
+        <v>2</v>
+      </c>
+      <c r="J97" s="1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:10">
       <c r="A98" s="2">
         <v>46057</v>
       </c>
+      <c r="B98" s="1">
+        <v>1245</v>
+      </c>
+      <c r="C98" s="1">
+        <v>884</v>
+      </c>
       <c r="D98" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="1:4">
+        <v>361</v>
+      </c>
+      <c r="E98" s="1">
+        <v>63</v>
+      </c>
+      <c r="F98" s="1">
+        <v>3</v>
+      </c>
+      <c r="G98" s="1">
+        <v>4</v>
+      </c>
+      <c r="H98" s="1">
+        <v>50</v>
+      </c>
+      <c r="I98" s="1">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:10">
       <c r="A99" s="2">
         <v>46058</v>
       </c>
+      <c r="B99" s="1">
+        <v>6805</v>
+      </c>
+      <c r="C99" s="1">
+        <v>6380</v>
+      </c>
       <c r="D99" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="1:4">
+        <v>425</v>
+      </c>
+      <c r="E99" s="1">
+        <v>117</v>
+      </c>
+      <c r="F99" s="1">
+        <v>3</v>
+      </c>
+      <c r="G99" s="1">
+        <v>4</v>
+      </c>
+      <c r="H99" s="1">
+        <v>204</v>
+      </c>
+      <c r="I99" s="1">
+        <v>3</v>
+      </c>
+      <c r="J99" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:10">
       <c r="A100" s="2">
         <v>46059</v>
       </c>
@@ -4253,7 +4469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="1:4">
+    <row r="101" customHeight="1" spans="1:10">
       <c r="A101" s="2">
         <v>46060</v>
       </c>
@@ -4262,7 +4478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="1:4">
+    <row r="102" customHeight="1" spans="1:10">
       <c r="A102" s="2">
         <v>46061</v>
       </c>
@@ -4271,7 +4487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="1:4">
+    <row r="103" customHeight="1" spans="1:10">
       <c r="A103" s="2">
         <v>46062</v>
       </c>
@@ -4280,7 +4496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="1:4">
+    <row r="104" customHeight="1" spans="1:10">
       <c r="A104" s="2">
         <v>46063</v>
       </c>
@@ -4289,7 +4505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="1:4">
+    <row r="105" customHeight="1" spans="1:10">
       <c r="A105" s="2">
         <v>46064</v>
       </c>
@@ -4298,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" customHeight="1" spans="1:4">
+    <row r="106" customHeight="1" spans="1:10">
       <c r="A106" s="2">
         <v>46065</v>
       </c>
@@ -4307,7 +4523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="1:4">
+    <row r="107" customHeight="1" spans="1:10">
       <c r="A107" s="2">
         <v>46066</v>
       </c>
@@ -4316,7 +4532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="1:4">
+    <row r="108" customHeight="1" spans="1:10">
       <c r="A108" s="2">
         <v>46067</v>
       </c>
@@ -4325,7 +4541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="1:4">
+    <row r="109" customHeight="1" spans="1:10">
       <c r="A109" s="2">
         <v>46068</v>
       </c>
@@ -4334,7 +4550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="1:4">
+    <row r="110" customHeight="1" spans="1:10">
       <c r="A110" s="2">
         <v>46069</v>
       </c>
@@ -4343,7 +4559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="1:4">
+    <row r="111" customHeight="1" spans="1:10">
       <c r="A111" s="2">
         <v>46070</v>
       </c>
@@ -4352,7 +4568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="1:4">
+    <row r="112" customHeight="1" spans="1:10">
       <c r="A112" s="2">
         <v>46071</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="店铺数据" sheetId="2" r:id="rId1"/>
@@ -4540,17 +4540,67 @@
       <c r="A102" s="3">
         <v>46059</v>
       </c>
+      <c r="B102">
+        <v>5187</v>
+      </c>
+      <c r="C102">
+        <v>4821</v>
+      </c>
       <c r="D102">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>366</v>
+      </c>
+      <c r="E102">
+        <v>94</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <f>F102</f>
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>206</v>
+      </c>
+      <c r="I102">
+        <v>8</v>
+      </c>
+      <c r="J102">
+        <v>23</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:10">
       <c r="A103" s="3">
         <v>46060</v>
       </c>
+      <c r="B103">
+        <v>5269</v>
+      </c>
+      <c r="C103">
+        <v>4940</v>
+      </c>
       <c r="D103">
         <f t="shared" si="4"/>
+        <v>329</v>
+      </c>
+      <c r="E103">
+        <v>104</v>
+      </c>
+      <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="G103">
+        <f t="shared" ref="G103:G134" si="5">F103</f>
+        <v>3</v>
+      </c>
+      <c r="H103">
+        <v>184</v>
+      </c>
+      <c r="I103">
+        <v>5</v>
+      </c>
+      <c r="J103">
         <v>0</v>
       </c>
     </row>
@@ -4558,8 +4608,33 @@
       <c r="A104" s="3">
         <v>46061</v>
       </c>
+      <c r="B104">
+        <v>321</v>
+      </c>
+      <c r="C104">
+        <v>13</v>
+      </c>
       <c r="D104">
         <f t="shared" si="4"/>
+        <v>308</v>
+      </c>
+      <c r="E104">
+        <v>23</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
         <v>0</v>
       </c>
     </row>
@@ -4567,8 +4642,33 @@
       <c r="A105" s="3">
         <v>46062</v>
       </c>
+      <c r="B105">
+        <v>7379</v>
+      </c>
+      <c r="C105">
+        <v>7004</v>
+      </c>
       <c r="D105">
         <f t="shared" si="4"/>
+        <v>375</v>
+      </c>
+      <c r="E105">
+        <v>42</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>68</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
         <v>0</v>
       </c>
     </row>
@@ -4576,8 +4676,33 @@
       <c r="A106" s="3">
         <v>46063</v>
       </c>
+      <c r="B106">
+        <v>333</v>
+      </c>
+      <c r="C106">
+        <v>28</v>
+      </c>
       <c r="D106">
         <f t="shared" si="4"/>
+        <v>305</v>
+      </c>
+      <c r="E106">
+        <v>11</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
         <v>0</v>
       </c>
     </row>
@@ -4585,17 +4710,67 @@
       <c r="A107" s="3">
         <v>46064</v>
       </c>
+      <c r="B107">
+        <v>277</v>
+      </c>
+      <c r="C107">
+        <v>15</v>
+      </c>
       <c r="D107">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>262</v>
+      </c>
+      <c r="E107">
+        <v>9</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>95</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:10">
       <c r="A108" s="3">
         <v>46065</v>
       </c>
+      <c r="B108">
+        <v>343</v>
+      </c>
+      <c r="C108">
+        <v>35</v>
+      </c>
       <c r="D108">
         <f t="shared" si="4"/>
+        <v>308</v>
+      </c>
+      <c r="E108">
+        <v>9</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
         <v>0</v>
       </c>
     </row>
@@ -4603,8 +4778,33 @@
       <c r="A109" s="3">
         <v>46066</v>
       </c>
+      <c r="B109">
+        <v>243</v>
+      </c>
+      <c r="C109">
+        <v>44</v>
+      </c>
       <c r="D109">
         <f t="shared" si="4"/>
+        <v>199</v>
+      </c>
+      <c r="E109">
+        <v>9</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
         <v>0</v>
       </c>
     </row>
@@ -4612,8 +4812,33 @@
       <c r="A110" s="3">
         <v>46067</v>
       </c>
+      <c r="B110">
+        <v>108</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
       <c r="D110">
         <f t="shared" si="4"/>
+        <v>106</v>
+      </c>
+      <c r="E110">
+        <v>7</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
         <v>0</v>
       </c>
     </row>
@@ -4621,8 +4846,33 @@
       <c r="A111" s="3">
         <v>46068</v>
       </c>
+      <c r="B111">
+        <v>186</v>
+      </c>
+      <c r="C111">
+        <v>7</v>
+      </c>
       <c r="D111">
         <f t="shared" si="4"/>
+        <v>179</v>
+      </c>
+      <c r="E111">
+        <v>23</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
         <v>0</v>
       </c>
     </row>
@@ -4630,1281 +4880,3979 @@
       <c r="A112" s="3">
         <v>46069</v>
       </c>
+      <c r="B112">
+        <v>127</v>
+      </c>
+      <c r="C112">
+        <v>7</v>
+      </c>
       <c r="D112">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="1:4">
+        <v>120</v>
+      </c>
+      <c r="E112">
+        <v>5</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:10">
       <c r="A113" s="3">
         <v>46070</v>
       </c>
+      <c r="B113">
+        <v>123</v>
+      </c>
+      <c r="C113">
+        <v>14</v>
+      </c>
       <c r="D113">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" spans="1:4">
+        <v>109</v>
+      </c>
+      <c r="E113">
+        <v>3</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="1:10">
       <c r="A114" s="3">
         <v>46071</v>
       </c>
+      <c r="B114">
+        <v>125</v>
+      </c>
+      <c r="C114">
+        <v>12</v>
+      </c>
       <c r="D114">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" spans="1:4">
+        <v>113</v>
+      </c>
+      <c r="E114">
+        <v>4</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="1:10">
       <c r="A115" s="3">
         <v>46072</v>
       </c>
+      <c r="B115">
+        <v>72</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
       <c r="D115">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" spans="1:4">
+        <v>71</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="1:10">
       <c r="A116" s="3">
         <v>46073</v>
       </c>
+      <c r="B116">
+        <v>77</v>
+      </c>
+      <c r="C116">
+        <v>5</v>
+      </c>
       <c r="D116">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="1:4">
+        <v>72</v>
+      </c>
+      <c r="E116">
+        <v>4</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="1:10">
       <c r="A117" s="3">
         <v>46074</v>
       </c>
+      <c r="B117">
+        <v>173</v>
+      </c>
+      <c r="C117">
+        <v>12</v>
+      </c>
       <c r="D117">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" spans="1:4">
+        <v>161</v>
+      </c>
+      <c r="E117">
+        <v>7</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="1:10">
       <c r="A118" s="3">
         <v>46075</v>
       </c>
+      <c r="B118">
+        <v>154</v>
+      </c>
+      <c r="C118">
+        <v>16</v>
+      </c>
       <c r="D118">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" spans="1:4">
+        <v>138</v>
+      </c>
+      <c r="E118">
+        <v>7</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="1:10">
       <c r="A119" s="3">
         <v>46076</v>
       </c>
+      <c r="B119">
+        <v>242</v>
+      </c>
+      <c r="C119">
+        <v>16</v>
+      </c>
       <c r="D119">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" spans="1:4">
+        <v>226</v>
+      </c>
+      <c r="E119">
+        <v>10</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>34</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="1:10">
       <c r="A120" s="3">
         <v>46077</v>
       </c>
+      <c r="B120">
+        <v>373</v>
+      </c>
+      <c r="C120">
+        <v>15</v>
+      </c>
       <c r="D120">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" spans="1:4">
+        <v>358</v>
+      </c>
+      <c r="E120">
+        <v>12</v>
+      </c>
+      <c r="F120">
+        <v>3</v>
+      </c>
+      <c r="G120">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H120">
+        <v>34</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="1:10">
       <c r="A121" s="3">
         <v>46078</v>
       </c>
+      <c r="B121">
+        <v>2264</v>
+      </c>
+      <c r="C121">
+        <v>1842</v>
+      </c>
       <c r="D121">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" customHeight="1" spans="1:4">
+        <v>422</v>
+      </c>
+      <c r="E121">
+        <v>91</v>
+      </c>
+      <c r="F121">
+        <v>4</v>
+      </c>
+      <c r="G121">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="H121">
+        <v>117</v>
+      </c>
+      <c r="I121">
+        <v>16</v>
+      </c>
+      <c r="J121">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="1:10">
       <c r="A122" s="3">
         <v>46079</v>
       </c>
+      <c r="B122">
+        <v>5342</v>
+      </c>
+      <c r="C122">
+        <v>4542</v>
+      </c>
       <c r="D122">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" spans="1:4">
+        <v>800</v>
+      </c>
+      <c r="E122">
+        <v>122</v>
+      </c>
+      <c r="F122">
+        <v>7</v>
+      </c>
+      <c r="G122">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="H122">
+        <v>204</v>
+      </c>
+      <c r="I122">
+        <v>5</v>
+      </c>
+      <c r="J122">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="1:10">
       <c r="A123" s="3">
         <v>46080</v>
       </c>
+      <c r="B123">
+        <v>6488</v>
+      </c>
+      <c r="C123">
+        <v>5913</v>
+      </c>
       <c r="D123">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" spans="1:4">
+        <v>575</v>
+      </c>
+      <c r="E123">
+        <v>116</v>
+      </c>
+      <c r="F123">
+        <v>8</v>
+      </c>
+      <c r="G123">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="H123">
+        <v>200</v>
+      </c>
+      <c r="I123">
+        <v>12</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="1:10">
       <c r="A124" s="3">
         <v>46081</v>
       </c>
+      <c r="B124">
+        <v>4919</v>
+      </c>
+      <c r="C124">
+        <v>4326</v>
+      </c>
       <c r="D124">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" spans="1:4">
+        <v>593</v>
+      </c>
+      <c r="E124">
+        <v>99</v>
+      </c>
+      <c r="F124">
+        <v>5</v>
+      </c>
+      <c r="G124">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H124">
+        <v>208</v>
+      </c>
+      <c r="I124">
+        <v>5</v>
+      </c>
+      <c r="J124">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="1:10">
       <c r="A125" s="3">
         <v>46082</v>
       </c>
+      <c r="B125">
+        <v>363</v>
+      </c>
+      <c r="C125">
+        <v>29</v>
+      </c>
       <c r="D125">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" customHeight="1" spans="1:4">
+        <v>334</v>
+      </c>
+      <c r="E125">
+        <v>10</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>34</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="1:10">
       <c r="A126" s="3">
         <v>46083</v>
       </c>
+      <c r="B126">
+        <v>3438</v>
+      </c>
+      <c r="C126">
+        <v>3026</v>
+      </c>
       <c r="D126">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" spans="1:4">
+        <v>412</v>
+      </c>
+      <c r="E126">
+        <v>93</v>
+      </c>
+      <c r="F126">
+        <v>6</v>
+      </c>
+      <c r="G126">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H126">
+        <v>163</v>
+      </c>
+      <c r="I126">
+        <v>5</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:10">
       <c r="A127" s="3">
         <v>46084</v>
       </c>
+      <c r="B127">
+        <v>3207</v>
+      </c>
+      <c r="C127">
+        <v>2849</v>
+      </c>
       <c r="D127">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" spans="1:4">
+        <v>358</v>
+      </c>
+      <c r="E127">
+        <v>82</v>
+      </c>
+      <c r="F127">
+        <v>3</v>
+      </c>
+      <c r="G127">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H127">
+        <v>169</v>
+      </c>
+      <c r="I127">
+        <v>7</v>
+      </c>
+      <c r="J127">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:10">
       <c r="A128" s="3">
         <v>46085</v>
       </c>
+      <c r="B128">
+        <v>3144</v>
+      </c>
+      <c r="C128">
+        <v>2805</v>
+      </c>
       <c r="D128">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" spans="1:4">
+        <v>339</v>
+      </c>
+      <c r="E128">
+        <v>93</v>
+      </c>
+      <c r="F128">
+        <v>2</v>
+      </c>
+      <c r="G128">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H128">
+        <v>188</v>
+      </c>
+      <c r="I128">
+        <v>3</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="1:10">
       <c r="A129" s="3">
         <v>46086</v>
       </c>
+      <c r="B129">
+        <v>3806</v>
+      </c>
+      <c r="C129">
+        <v>3428</v>
+      </c>
       <c r="D129">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" spans="1:4">
+        <v>378</v>
+      </c>
+      <c r="E129">
+        <v>136</v>
+      </c>
+      <c r="F129">
+        <v>4</v>
+      </c>
+      <c r="G129">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="H129">
+        <v>189</v>
+      </c>
+      <c r="I129">
+        <v>3</v>
+      </c>
+      <c r="J129">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="1:10">
       <c r="A130" s="3">
         <v>46087</v>
       </c>
+      <c r="B130">
+        <v>4634</v>
+      </c>
+      <c r="C130">
+        <v>4274</v>
+      </c>
       <c r="D130">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" spans="1:4">
+        <v>360</v>
+      </c>
+      <c r="E130">
+        <v>138</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H130">
+        <v>184</v>
+      </c>
+      <c r="I130">
+        <v>4</v>
+      </c>
+      <c r="J130">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="1:10">
       <c r="A131" s="3">
         <v>46088</v>
       </c>
-    </row>
-    <row r="132" customHeight="1" spans="1:4">
+      <c r="B131">
+        <v>2732</v>
+      </c>
+      <c r="C131">
+        <v>2423</v>
+      </c>
+      <c r="D131">
+        <f t="shared" ref="D131:D162" si="6">B131-C131</f>
+        <v>309</v>
+      </c>
+      <c r="E131">
+        <v>104</v>
+      </c>
+      <c r="F131">
+        <v>2</v>
+      </c>
+      <c r="G131">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H131">
+        <v>163</v>
+      </c>
+      <c r="I131">
+        <v>6</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="1:10">
       <c r="A132" s="3">
         <v>46089</v>
       </c>
-    </row>
-    <row r="133" customHeight="1" spans="1:4">
+      <c r="B132">
+        <v>1543</v>
+      </c>
+      <c r="C132">
+        <v>1294</v>
+      </c>
+      <c r="D132">
+        <f t="shared" si="6"/>
+        <v>249</v>
+      </c>
+      <c r="E132">
+        <v>38</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H132">
+        <v>151</v>
+      </c>
+      <c r="I132">
+        <v>5</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="1:10">
       <c r="A133" s="3">
         <v>46090</v>
       </c>
-    </row>
-    <row r="134" customHeight="1" spans="1:4">
+      <c r="B133">
+        <v>2787</v>
+      </c>
+      <c r="C133">
+        <v>2483</v>
+      </c>
+      <c r="D133">
+        <f t="shared" si="6"/>
+        <v>304</v>
+      </c>
+      <c r="E133">
+        <v>101</v>
+      </c>
+      <c r="F133">
+        <v>3</v>
+      </c>
+      <c r="G133">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H133">
+        <v>204</v>
+      </c>
+      <c r="I133">
+        <v>4</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="1:10">
       <c r="A134" s="3">
         <v>46091</v>
       </c>
-    </row>
-    <row r="135" customHeight="1" spans="1:4">
+      <c r="B134">
+        <v>3518</v>
+      </c>
+      <c r="C134">
+        <v>3165</v>
+      </c>
+      <c r="D134">
+        <f t="shared" si="6"/>
+        <v>353</v>
+      </c>
+      <c r="E134">
+        <v>105</v>
+      </c>
+      <c r="F134">
+        <v>6</v>
+      </c>
+      <c r="G134">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H134">
+        <v>196</v>
+      </c>
+      <c r="I134">
+        <v>13</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="1:10">
       <c r="A135" s="3">
         <v>46092</v>
       </c>
-    </row>
-    <row r="136" customHeight="1" spans="1:4">
+      <c r="B135">
+        <v>3524</v>
+      </c>
+      <c r="C135">
+        <v>3022</v>
+      </c>
+      <c r="D135">
+        <f t="shared" si="6"/>
+        <v>502</v>
+      </c>
+      <c r="E135">
+        <v>128</v>
+      </c>
+      <c r="F135">
+        <v>8</v>
+      </c>
+      <c r="G135">
+        <f t="shared" ref="G135:G154" si="7">F135</f>
+        <v>8</v>
+      </c>
+      <c r="H135">
+        <v>207</v>
+      </c>
+      <c r="I135">
+        <v>8</v>
+      </c>
+      <c r="J135">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="1:10">
       <c r="A136" s="3">
         <v>46093</v>
       </c>
-    </row>
-    <row r="137" customHeight="1" spans="1:4">
+      <c r="B136">
+        <v>3720</v>
+      </c>
+      <c r="C136">
+        <v>3043</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="6"/>
+        <v>677</v>
+      </c>
+      <c r="E136">
+        <v>106</v>
+      </c>
+      <c r="F136">
+        <v>4</v>
+      </c>
+      <c r="G136">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H136">
+        <v>198</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="1:10">
       <c r="A137" s="3">
         <v>46094</v>
       </c>
-    </row>
-    <row r="138" customHeight="1" spans="1:4">
+      <c r="B137">
+        <v>2255</v>
+      </c>
+      <c r="C137">
+        <v>1739</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="6"/>
+        <v>516</v>
+      </c>
+      <c r="E137">
+        <v>80</v>
+      </c>
+      <c r="F137">
+        <v>3</v>
+      </c>
+      <c r="G137">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="H137">
+        <v>178</v>
+      </c>
+      <c r="I137">
+        <v>6</v>
+      </c>
+      <c r="J137">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="1:10">
       <c r="A138" s="3">
         <v>46095</v>
       </c>
-    </row>
-    <row r="139" customHeight="1" spans="1:4">
+      <c r="B138">
+        <v>1476</v>
+      </c>
+      <c r="C138">
+        <v>1151</v>
+      </c>
+      <c r="D138">
+        <f t="shared" si="6"/>
+        <v>325</v>
+      </c>
+      <c r="E138">
+        <v>887</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>74</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="1:10">
       <c r="A139" s="3">
         <v>46096</v>
       </c>
-    </row>
-    <row r="140" customHeight="1" spans="1:4">
+      <c r="B139">
+        <v>289</v>
+      </c>
+      <c r="C139">
+        <v>45</v>
+      </c>
+      <c r="D139">
+        <f t="shared" si="6"/>
+        <v>244</v>
+      </c>
+      <c r="E139">
+        <v>13</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>34</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="1:10">
       <c r="A140" s="3">
         <v>46097</v>
       </c>
-    </row>
-    <row r="141" customHeight="1" spans="1:4">
+      <c r="B140">
+        <v>3739</v>
+      </c>
+      <c r="C140">
+        <v>2240</v>
+      </c>
+      <c r="D140">
+        <f t="shared" si="6"/>
+        <v>1499</v>
+      </c>
+      <c r="E140">
+        <v>80</v>
+      </c>
+      <c r="F140">
+        <v>5</v>
+      </c>
+      <c r="G140">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="H140">
+        <v>201</v>
+      </c>
+      <c r="I140">
+        <v>8</v>
+      </c>
+      <c r="J140">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="1:10">
       <c r="A141" s="3">
         <v>46098</v>
       </c>
-    </row>
-    <row r="142" customHeight="1" spans="1:4">
+      <c r="B141">
+        <v>2923</v>
+      </c>
+      <c r="C141">
+        <v>2376</v>
+      </c>
+      <c r="D141">
+        <f t="shared" si="6"/>
+        <v>547</v>
+      </c>
+      <c r="E141">
+        <v>119</v>
+      </c>
+      <c r="F141">
+        <v>3</v>
+      </c>
+      <c r="G141">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="H141">
+        <v>204</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="1:10">
       <c r="A142" s="3">
         <v>46099</v>
       </c>
-    </row>
-    <row r="143" customHeight="1" spans="1:4">
+      <c r="B142">
+        <v>4581</v>
+      </c>
+      <c r="C142">
+        <v>4102</v>
+      </c>
+      <c r="D142">
+        <f t="shared" si="6"/>
+        <v>479</v>
+      </c>
+      <c r="E142">
+        <v>75</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>190</v>
+      </c>
+      <c r="I142">
+        <v>3</v>
+      </c>
+      <c r="J142">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="1:10">
       <c r="A143" s="3">
         <v>46100</v>
       </c>
-    </row>
-    <row r="144" customHeight="1" spans="1:4">
+      <c r="B143">
+        <v>3646</v>
+      </c>
+      <c r="C143">
+        <v>3176</v>
+      </c>
+      <c r="D143">
+        <f t="shared" si="6"/>
+        <v>470</v>
+      </c>
+      <c r="E143">
+        <v>115</v>
+      </c>
+      <c r="F143">
+        <v>4</v>
+      </c>
+      <c r="G143">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H143">
+        <v>202</v>
+      </c>
+      <c r="I143">
+        <v>4</v>
+      </c>
+      <c r="J143">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:10">
       <c r="A144" s="3">
         <v>46101</v>
       </c>
-    </row>
-    <row r="145" customHeight="1" spans="1:1">
+      <c r="B144">
+        <v>4482</v>
+      </c>
+      <c r="C144">
+        <v>3933</v>
+      </c>
+      <c r="D144">
+        <f t="shared" si="6"/>
+        <v>549</v>
+      </c>
+      <c r="E144">
+        <v>106</v>
+      </c>
+      <c r="F144">
+        <v>7</v>
+      </c>
+      <c r="G144">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="H144">
+        <v>191</v>
+      </c>
+      <c r="I144">
+        <v>5</v>
+      </c>
+      <c r="J144">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="1:10">
       <c r="A145" s="3">
         <v>46102</v>
       </c>
-    </row>
-    <row r="146" customHeight="1" spans="1:1">
+      <c r="B145">
+        <v>3016</v>
+      </c>
+      <c r="C145">
+        <v>2710</v>
+      </c>
+      <c r="D145">
+        <f t="shared" si="6"/>
+        <v>306</v>
+      </c>
+      <c r="E145">
+        <v>107</v>
+      </c>
+      <c r="F145">
+        <v>2</v>
+      </c>
+      <c r="G145">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="H145">
+        <v>186</v>
+      </c>
+      <c r="I145">
+        <v>4</v>
+      </c>
+      <c r="J145">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="1:10">
       <c r="A146" s="3">
         <v>46103</v>
       </c>
-    </row>
-    <row r="147" customHeight="1" spans="1:1">
+      <c r="B146">
+        <v>282</v>
+      </c>
+      <c r="C146">
+        <v>38</v>
+      </c>
+      <c r="D146">
+        <f t="shared" si="6"/>
+        <v>244</v>
+      </c>
+      <c r="E146">
+        <v>23</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>34</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="1:10">
       <c r="A147" s="3">
         <v>46104</v>
       </c>
-    </row>
-    <row r="148" customHeight="1" spans="1:1">
+      <c r="B147">
+        <v>3809</v>
+      </c>
+      <c r="C147">
+        <v>3468</v>
+      </c>
+      <c r="D147">
+        <f t="shared" si="6"/>
+        <v>341</v>
+      </c>
+      <c r="E147">
+        <v>119</v>
+      </c>
+      <c r="F147">
+        <v>4</v>
+      </c>
+      <c r="G147">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H147">
+        <v>190</v>
+      </c>
+      <c r="I147">
+        <v>9</v>
+      </c>
+      <c r="J147">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="1:10">
       <c r="A148" s="3">
         <v>46105</v>
       </c>
-    </row>
-    <row r="149" customHeight="1" spans="1:1">
+      <c r="B148">
+        <v>4501</v>
+      </c>
+      <c r="C148">
+        <v>4028</v>
+      </c>
+      <c r="D148">
+        <f t="shared" si="6"/>
+        <v>473</v>
+      </c>
+      <c r="E148">
+        <v>127</v>
+      </c>
+      <c r="F148">
+        <v>3</v>
+      </c>
+      <c r="G148">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="H148">
+        <v>211</v>
+      </c>
+      <c r="I148">
+        <v>5</v>
+      </c>
+      <c r="J148">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="1:10">
       <c r="A149" s="3">
         <v>46106</v>
       </c>
-    </row>
-    <row r="150" customHeight="1" spans="1:1">
+      <c r="B149">
+        <v>4345</v>
+      </c>
+      <c r="C149">
+        <v>3954</v>
+      </c>
+      <c r="D149">
+        <f t="shared" si="6"/>
+        <v>391</v>
+      </c>
+      <c r="E149">
+        <v>159</v>
+      </c>
+      <c r="F149">
+        <v>7</v>
+      </c>
+      <c r="G149">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="H149">
+        <v>211</v>
+      </c>
+      <c r="I149">
+        <v>8</v>
+      </c>
+      <c r="J149">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="1:10">
       <c r="A150" s="3">
         <v>46107</v>
       </c>
-    </row>
-    <row r="151" customHeight="1" spans="1:1">
+      <c r="B150">
+        <v>4666</v>
+      </c>
+      <c r="C150">
+        <v>4175</v>
+      </c>
+      <c r="D150">
+        <f t="shared" si="6"/>
+        <v>491</v>
+      </c>
+      <c r="E150">
+        <v>143</v>
+      </c>
+      <c r="F150">
+        <v>7</v>
+      </c>
+      <c r="G150">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="H150">
+        <v>243</v>
+      </c>
+      <c r="I150">
+        <v>6</v>
+      </c>
+      <c r="J150">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="1:10">
       <c r="A151" s="3">
         <v>46108</v>
       </c>
-    </row>
-    <row r="152" customHeight="1" spans="1:1">
+      <c r="B151">
+        <v>5914</v>
+      </c>
+      <c r="C151">
+        <v>4837</v>
+      </c>
+      <c r="D151">
+        <f t="shared" si="6"/>
+        <v>1077</v>
+      </c>
+      <c r="E151">
+        <v>122</v>
+      </c>
+      <c r="F151">
+        <v>6</v>
+      </c>
+      <c r="G151">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H151">
+        <v>220</v>
+      </c>
+      <c r="I151">
+        <v>10</v>
+      </c>
+      <c r="J151">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="1:10">
       <c r="A152" s="3">
         <v>46109</v>
       </c>
-    </row>
-    <row r="153" customHeight="1" spans="1:1">
+      <c r="B152">
+        <v>3909</v>
+      </c>
+      <c r="C152">
+        <v>3398</v>
+      </c>
+      <c r="D152">
+        <f t="shared" si="6"/>
+        <v>511</v>
+      </c>
+      <c r="E152">
+        <v>127</v>
+      </c>
+      <c r="F152">
+        <v>4</v>
+      </c>
+      <c r="G152">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H152">
+        <v>180</v>
+      </c>
+      <c r="I152">
+        <v>7</v>
+      </c>
+      <c r="J152">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="1:10">
       <c r="A153" s="3">
         <v>46110</v>
       </c>
-    </row>
-    <row r="154" customHeight="1" spans="1:1">
+      <c r="B153">
+        <v>448</v>
+      </c>
+      <c r="C153">
+        <v>38</v>
+      </c>
+      <c r="D153">
+        <f t="shared" si="6"/>
+        <v>410</v>
+      </c>
+      <c r="E153">
+        <v>24</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+      <c r="G153">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="H153">
+        <v>35</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
+      <c r="J153">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="1:10">
       <c r="A154" s="3">
         <v>46111</v>
       </c>
-    </row>
-    <row r="155" customHeight="1" spans="1:1">
+      <c r="B154">
+        <v>4401</v>
+      </c>
+      <c r="C154">
+        <v>3976</v>
+      </c>
+      <c r="D154">
+        <f t="shared" si="6"/>
+        <v>425</v>
+      </c>
+      <c r="E154">
+        <v>116</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>188</v>
+      </c>
+      <c r="I154">
+        <v>5</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="1:10">
       <c r="A155" s="3">
         <v>46112</v>
       </c>
-    </row>
-    <row r="156" customHeight="1" spans="1:1">
+      <c r="B155">
+        <v>3787</v>
+      </c>
+      <c r="C155">
+        <v>3122</v>
+      </c>
+      <c r="D155">
+        <f t="shared" si="6"/>
+        <v>665</v>
+      </c>
+      <c r="E155">
+        <v>75</v>
+      </c>
+      <c r="F155">
+        <v>3</v>
+      </c>
+      <c r="G155">
+        <f t="shared" ref="G155:G186" si="8">F155</f>
+        <v>3</v>
+      </c>
+      <c r="H155">
+        <v>201</v>
+      </c>
+      <c r="I155">
+        <v>5</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="1:10">
       <c r="A156" s="3">
         <v>46113</v>
       </c>
-    </row>
-    <row r="157" customHeight="1" spans="1:1">
+      <c r="B156">
+        <v>4539</v>
+      </c>
+      <c r="C156">
+        <v>4122</v>
+      </c>
+      <c r="D156">
+        <f t="shared" si="6"/>
+        <v>417</v>
+      </c>
+      <c r="E156">
+        <v>128</v>
+      </c>
+      <c r="F156">
+        <v>4</v>
+      </c>
+      <c r="G156">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="H156">
+        <v>142</v>
+      </c>
+      <c r="I156">
+        <v>9</v>
+      </c>
+      <c r="J156">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="1:10">
       <c r="A157" s="3">
         <v>46114</v>
       </c>
-    </row>
-    <row r="158" customHeight="1" spans="1:1">
+      <c r="B157">
+        <v>4579</v>
+      </c>
+      <c r="C157">
+        <v>4162</v>
+      </c>
+      <c r="D157">
+        <f t="shared" si="6"/>
+        <v>417</v>
+      </c>
+      <c r="E157">
+        <v>119</v>
+      </c>
+      <c r="F157">
+        <v>8</v>
+      </c>
+      <c r="G157">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="H157">
+        <v>207</v>
+      </c>
+      <c r="I157">
+        <v>8</v>
+      </c>
+      <c r="J157">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="1:10">
       <c r="A158" s="3">
         <v>46115</v>
       </c>
-    </row>
-    <row r="159" customHeight="1" spans="1:1">
+      <c r="B158">
+        <v>5944</v>
+      </c>
+      <c r="C158">
+        <v>5522</v>
+      </c>
+      <c r="D158">
+        <f t="shared" si="6"/>
+        <v>422</v>
+      </c>
+      <c r="E158">
+        <v>157</v>
+      </c>
+      <c r="F158">
+        <v>5</v>
+      </c>
+      <c r="G158">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H158">
+        <v>218</v>
+      </c>
+      <c r="I158">
+        <v>6</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="1:10">
       <c r="A159" s="3">
         <v>46116</v>
       </c>
-    </row>
-    <row r="160" customHeight="1" spans="1:1">
+      <c r="B159">
+        <v>4104</v>
+      </c>
+      <c r="C159">
+        <v>3685</v>
+      </c>
+      <c r="D159">
+        <f t="shared" si="6"/>
+        <v>419</v>
+      </c>
+      <c r="E159">
+        <v>61</v>
+      </c>
+      <c r="F159">
+        <v>2</v>
+      </c>
+      <c r="G159">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="H159">
+        <v>184</v>
+      </c>
+      <c r="I159">
+        <v>6</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="1:10">
       <c r="A160" s="3">
         <v>46117</v>
       </c>
-    </row>
-    <row r="161" customHeight="1" spans="1:1">
+      <c r="B160">
+        <v>1652</v>
+      </c>
+      <c r="C160">
+        <v>1459</v>
+      </c>
+      <c r="D160">
+        <f t="shared" si="6"/>
+        <v>193</v>
+      </c>
+      <c r="E160">
+        <v>29</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H160">
+        <v>155</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="1:10">
       <c r="A161" s="3">
         <v>46118</v>
       </c>
-    </row>
-    <row r="162" customHeight="1" spans="1:1">
+      <c r="B161">
+        <v>4216</v>
+      </c>
+      <c r="C161">
+        <v>3880</v>
+      </c>
+      <c r="D161">
+        <f t="shared" si="6"/>
+        <v>336</v>
+      </c>
+      <c r="E161">
+        <v>72</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H161">
+        <v>156</v>
+      </c>
+      <c r="I161">
+        <v>2</v>
+      </c>
+      <c r="J161">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="1:10">
       <c r="A162" s="3">
         <v>46119</v>
       </c>
-    </row>
-    <row r="163" customHeight="1" spans="1:1">
+      <c r="B162">
+        <v>5754</v>
+      </c>
+      <c r="C162">
+        <v>5352</v>
+      </c>
+      <c r="D162">
+        <f t="shared" si="6"/>
+        <v>402</v>
+      </c>
+      <c r="E162">
+        <v>147</v>
+      </c>
+      <c r="F162">
+        <v>5</v>
+      </c>
+      <c r="G162">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H162">
+        <v>175</v>
+      </c>
+      <c r="I162">
+        <v>11</v>
+      </c>
+      <c r="J162">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="1:10">
       <c r="A163" s="3">
         <v>46120</v>
       </c>
-    </row>
-    <row r="164" customHeight="1" spans="1:1">
+      <c r="B163">
+        <v>6691</v>
+      </c>
+      <c r="C163">
+        <v>6187</v>
+      </c>
+      <c r="D163">
+        <f t="shared" ref="D163:D184" si="9">B163-C163</f>
+        <v>504</v>
+      </c>
+      <c r="E163">
+        <v>175</v>
+      </c>
+      <c r="F163">
+        <v>4</v>
+      </c>
+      <c r="G163">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="H163">
+        <v>204</v>
+      </c>
+      <c r="I163">
+        <v>6</v>
+      </c>
+      <c r="J163">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="1:10">
       <c r="A164" s="3">
         <v>46121</v>
       </c>
-    </row>
-    <row r="165" customHeight="1" spans="1:1">
+      <c r="B164">
+        <v>4648</v>
+      </c>
+      <c r="C164">
+        <v>4175</v>
+      </c>
+      <c r="D164">
+        <f t="shared" si="9"/>
+        <v>473</v>
+      </c>
+      <c r="E164">
+        <v>152</v>
+      </c>
+      <c r="F164">
+        <v>3</v>
+      </c>
+      <c r="G164">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="H164">
+        <v>228</v>
+      </c>
+      <c r="I164">
+        <v>3</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="1:10">
       <c r="A165" s="3">
         <v>46122</v>
       </c>
-    </row>
-    <row r="166" customHeight="1" spans="1:1">
+      <c r="B165">
+        <v>4416</v>
+      </c>
+      <c r="C165">
+        <v>3904</v>
+      </c>
+      <c r="D165">
+        <f t="shared" si="9"/>
+        <v>512</v>
+      </c>
+      <c r="E165">
+        <v>130</v>
+      </c>
+      <c r="F165">
+        <v>5</v>
+      </c>
+      <c r="G165">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H165">
+        <v>240</v>
+      </c>
+      <c r="I165">
+        <v>20</v>
+      </c>
+      <c r="J165">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="1:10">
       <c r="A166" s="3">
         <v>46123</v>
       </c>
-    </row>
-    <row r="167" customHeight="1" spans="1:1">
+      <c r="B166">
+        <v>5061</v>
+      </c>
+      <c r="C166">
+        <v>4682</v>
+      </c>
+      <c r="D166">
+        <f t="shared" si="9"/>
+        <v>379</v>
+      </c>
+      <c r="E166">
+        <v>137</v>
+      </c>
+      <c r="F166">
+        <v>3</v>
+      </c>
+      <c r="G166">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="H166">
+        <v>223</v>
+      </c>
+      <c r="I166">
+        <v>6</v>
+      </c>
+      <c r="J166">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="1:10">
       <c r="A167" s="3">
         <v>46124</v>
       </c>
-    </row>
-    <row r="168" customHeight="1" spans="1:1">
+      <c r="B167">
+        <v>403</v>
+      </c>
+      <c r="C167">
+        <v>117</v>
+      </c>
+      <c r="D167">
+        <f t="shared" si="9"/>
+        <v>286</v>
+      </c>
+      <c r="E167">
+        <v>36</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="H167">
+        <v>35</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="1:10">
       <c r="A168" s="3">
         <v>46125</v>
       </c>
-    </row>
-    <row r="169" customHeight="1" spans="1:1">
+      <c r="B168">
+        <v>4491</v>
+      </c>
+      <c r="C168">
+        <v>3991</v>
+      </c>
+      <c r="D168">
+        <f t="shared" si="9"/>
+        <v>500</v>
+      </c>
+      <c r="E168">
+        <v>156</v>
+      </c>
+      <c r="F168">
+        <v>4</v>
+      </c>
+      <c r="G168">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="H168">
+        <v>222</v>
+      </c>
+      <c r="I168">
+        <v>6</v>
+      </c>
+      <c r="J168">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="1:10">
       <c r="A169" s="3">
         <v>46126</v>
       </c>
-    </row>
-    <row r="170" customHeight="1" spans="1:1">
+      <c r="B169">
+        <v>3942</v>
+      </c>
+      <c r="C169">
+        <v>3233</v>
+      </c>
+      <c r="D169">
+        <f t="shared" si="9"/>
+        <v>709</v>
+      </c>
+      <c r="E169">
+        <v>177</v>
+      </c>
+      <c r="F169">
+        <v>5</v>
+      </c>
+      <c r="G169">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H169">
+        <v>244</v>
+      </c>
+      <c r="I169">
+        <v>7</v>
+      </c>
+      <c r="J169">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="1:10">
       <c r="A170" s="3">
         <v>46127</v>
       </c>
-    </row>
-    <row r="171" customHeight="1" spans="1:1">
+      <c r="B170">
+        <v>3630</v>
+      </c>
+      <c r="C170">
+        <v>3018</v>
+      </c>
+      <c r="D170">
+        <f t="shared" si="9"/>
+        <v>612</v>
+      </c>
+      <c r="E170">
+        <v>130</v>
+      </c>
+      <c r="F170">
+        <v>2</v>
+      </c>
+      <c r="G170">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="H170">
+        <v>244</v>
+      </c>
+      <c r="I170">
+        <v>3</v>
+      </c>
+      <c r="J170">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="1:10">
       <c r="A171" s="3">
         <v>46128</v>
       </c>
-    </row>
-    <row r="172" customHeight="1" spans="1:1">
+      <c r="B171">
+        <v>4128</v>
+      </c>
+      <c r="C171">
+        <v>3643</v>
+      </c>
+      <c r="D171">
+        <f t="shared" si="9"/>
+        <v>485</v>
+      </c>
+      <c r="E171">
+        <v>127</v>
+      </c>
+      <c r="F171">
+        <v>5</v>
+      </c>
+      <c r="G171">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H171">
+        <v>220</v>
+      </c>
+      <c r="I171">
+        <v>12</v>
+      </c>
+      <c r="J171">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="1:10">
       <c r="A172" s="3">
         <v>46129</v>
       </c>
-    </row>
-    <row r="173" customHeight="1" spans="1:1">
+      <c r="B172">
+        <v>4378</v>
+      </c>
+      <c r="C172">
+        <v>3814</v>
+      </c>
+      <c r="D172">
+        <f t="shared" si="9"/>
+        <v>564</v>
+      </c>
+      <c r="E172">
+        <v>148</v>
+      </c>
+      <c r="F172">
+        <v>2</v>
+      </c>
+      <c r="G172">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="H172">
+        <v>242</v>
+      </c>
+      <c r="I172">
+        <v>4</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="1:10">
       <c r="A173" s="3">
         <v>46130</v>
       </c>
-    </row>
-    <row r="174" customHeight="1" spans="1:1">
+      <c r="B173">
+        <v>4394</v>
+      </c>
+      <c r="C173">
+        <v>4087</v>
+      </c>
+      <c r="D173">
+        <f t="shared" si="9"/>
+        <v>307</v>
+      </c>
+      <c r="E173">
+        <v>148</v>
+      </c>
+      <c r="F173">
+        <v>5</v>
+      </c>
+      <c r="G173">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H173">
+        <v>228</v>
+      </c>
+      <c r="I173">
+        <v>7</v>
+      </c>
+      <c r="J173">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="1:10">
       <c r="A174" s="3">
         <v>46131</v>
       </c>
-    </row>
-    <row r="175" customHeight="1" spans="1:1">
+      <c r="B174">
+        <v>1532</v>
+      </c>
+      <c r="C174">
+        <v>1248</v>
+      </c>
+      <c r="D174">
+        <f t="shared" si="9"/>
+        <v>284</v>
+      </c>
+      <c r="E174">
+        <v>55</v>
+      </c>
+      <c r="F174">
+        <v>0</v>
+      </c>
+      <c r="G174">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>155</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="1:10">
       <c r="A175" s="3">
         <v>46132</v>
       </c>
-    </row>
-    <row r="176" customHeight="1" spans="1:1">
+      <c r="B175">
+        <v>5400</v>
+      </c>
+      <c r="C175">
+        <v>4946</v>
+      </c>
+      <c r="D175">
+        <f t="shared" si="9"/>
+        <v>454</v>
+      </c>
+      <c r="E175">
+        <v>178</v>
+      </c>
+      <c r="F175">
+        <v>5</v>
+      </c>
+      <c r="G175">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H175">
+        <v>244</v>
+      </c>
+      <c r="I175">
+        <v>10</v>
+      </c>
+      <c r="J175">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="1:10">
       <c r="A176" s="3">
         <v>46133</v>
       </c>
-    </row>
-    <row r="177" customHeight="1" spans="1:1">
+      <c r="B176">
+        <v>5856</v>
+      </c>
+      <c r="C176">
+        <v>5342</v>
+      </c>
+      <c r="D176">
+        <f t="shared" si="9"/>
+        <v>514</v>
+      </c>
+      <c r="E176">
+        <v>161</v>
+      </c>
+      <c r="F176">
+        <v>4</v>
+      </c>
+      <c r="G176">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="H176">
+        <v>232</v>
+      </c>
+      <c r="I176">
+        <v>6</v>
+      </c>
+      <c r="J176">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" spans="1:10">
       <c r="A177" s="3">
         <v>46134</v>
       </c>
-    </row>
-    <row r="178" customHeight="1" spans="1:1">
+      <c r="B177">
+        <v>5083</v>
+      </c>
+      <c r="C177">
+        <v>4206</v>
+      </c>
+      <c r="D177">
+        <f t="shared" si="9"/>
+        <v>877</v>
+      </c>
+      <c r="E177">
+        <v>132</v>
+      </c>
+      <c r="F177">
+        <v>5</v>
+      </c>
+      <c r="G177">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H177">
+        <v>242</v>
+      </c>
+      <c r="I177">
+        <v>7</v>
+      </c>
+      <c r="J177">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" spans="1:10">
       <c r="A178" s="3">
         <v>46135</v>
       </c>
-    </row>
-    <row r="179" customHeight="1" spans="1:1">
+      <c r="B178">
+        <v>5800</v>
+      </c>
+      <c r="C178">
+        <v>5182</v>
+      </c>
+      <c r="D178">
+        <f t="shared" si="9"/>
+        <v>618</v>
+      </c>
+      <c r="E178">
+        <v>151</v>
+      </c>
+      <c r="F178">
+        <v>6</v>
+      </c>
+      <c r="G178">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="H178">
+        <v>245</v>
+      </c>
+      <c r="I178">
+        <v>8</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" spans="1:10">
       <c r="A179" s="3">
         <v>46136</v>
       </c>
-    </row>
-    <row r="180" customHeight="1" spans="1:1">
+      <c r="B179">
+        <v>5639</v>
+      </c>
+      <c r="C179">
+        <v>5071</v>
+      </c>
+      <c r="D179">
+        <f t="shared" si="9"/>
+        <v>568</v>
+      </c>
+      <c r="E179">
+        <v>173</v>
+      </c>
+      <c r="F179">
+        <v>4</v>
+      </c>
+      <c r="G179">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="H179">
+        <v>239</v>
+      </c>
+      <c r="I179">
+        <v>2</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="1:10">
       <c r="A180" s="3">
         <v>46137</v>
       </c>
-    </row>
-    <row r="181" customHeight="1" spans="1:1">
+      <c r="B180">
+        <v>4987</v>
+      </c>
+      <c r="C180">
+        <v>4420</v>
+      </c>
+      <c r="D180">
+        <f t="shared" si="9"/>
+        <v>567</v>
+      </c>
+      <c r="E180">
+        <v>133</v>
+      </c>
+      <c r="F180">
+        <v>7</v>
+      </c>
+      <c r="G180">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="H180">
+        <v>244</v>
+      </c>
+      <c r="I180">
+        <v>8</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="1:10">
       <c r="A181" s="3">
         <v>46138</v>
       </c>
-    </row>
-    <row r="182" customHeight="1" spans="1:1">
+      <c r="B181">
+        <v>984</v>
+      </c>
+      <c r="C181">
+        <v>665</v>
+      </c>
+      <c r="D181">
+        <f t="shared" si="9"/>
+        <v>319</v>
+      </c>
+      <c r="E181">
+        <v>35</v>
+      </c>
+      <c r="F181">
+        <v>2</v>
+      </c>
+      <c r="G181">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="H181">
+        <v>95</v>
+      </c>
+      <c r="I181">
+        <v>3</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="1:10">
       <c r="A182" s="3">
         <v>46139</v>
       </c>
-    </row>
-    <row r="183" customHeight="1" spans="1:1">
+      <c r="B182">
+        <v>5436</v>
+      </c>
+      <c r="C182">
+        <v>4894</v>
+      </c>
+      <c r="D182">
+        <f t="shared" si="9"/>
+        <v>542</v>
+      </c>
+      <c r="E182">
+        <v>143</v>
+      </c>
+      <c r="F182">
+        <v>2</v>
+      </c>
+      <c r="G182">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="H182">
+        <v>241</v>
+      </c>
+      <c r="I182">
+        <v>2</v>
+      </c>
+      <c r="J182">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="1:10">
       <c r="A183" s="3">
         <v>46140</v>
       </c>
-    </row>
-    <row r="184" customHeight="1" spans="1:1">
+      <c r="B183">
+        <v>5969</v>
+      </c>
+      <c r="C183">
+        <v>5537</v>
+      </c>
+      <c r="D183">
+        <f t="shared" si="9"/>
+        <v>432</v>
+      </c>
+      <c r="E183">
+        <v>119</v>
+      </c>
+      <c r="F183">
+        <v>7</v>
+      </c>
+      <c r="G183">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="H183">
+        <v>243</v>
+      </c>
+      <c r="I183">
+        <v>7</v>
+      </c>
+      <c r="J183">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="1:10">
       <c r="A184" s="3">
         <v>46141</v>
       </c>
-    </row>
-    <row r="185" customHeight="1" spans="1:1">
+      <c r="D184">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>234</v>
+      </c>
+      <c r="I184">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="1:10">
       <c r="A185" s="3">
         <v>46142</v>
       </c>
-    </row>
-    <row r="186" customHeight="1" spans="1:1">
+      <c r="G185">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="1:10">
       <c r="A186" s="3">
         <v>46143</v>
       </c>
-    </row>
-    <row r="187" customHeight="1" spans="1:1">
+      <c r="G186">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="1:10">
       <c r="A187" s="3">
         <v>46144</v>
       </c>
-    </row>
-    <row r="188" customHeight="1" spans="1:1">
+      <c r="G187">
+        <f t="shared" ref="G187:G218" si="10">F187</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="1:10">
       <c r="A188" s="3">
         <v>46145</v>
       </c>
-    </row>
-    <row r="189" customHeight="1" spans="1:1">
+      <c r="G188">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="1:10">
       <c r="A189" s="3">
         <v>46146</v>
       </c>
-    </row>
-    <row r="190" customHeight="1" spans="1:1">
+      <c r="G189">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="1:10">
       <c r="A190" s="3">
         <v>46147</v>
       </c>
-    </row>
-    <row r="191" customHeight="1" spans="1:1">
+      <c r="G190">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" spans="1:10">
       <c r="A191" s="3">
         <v>46148</v>
       </c>
-    </row>
-    <row r="192" customHeight="1" spans="1:1">
+      <c r="G191">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" spans="1:10">
       <c r="A192" s="3">
         <v>46149</v>
       </c>
-    </row>
-    <row r="193" customHeight="1" spans="1:1">
+      <c r="G192">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" spans="1:7">
       <c r="A193" s="3">
         <v>46150</v>
       </c>
-    </row>
-    <row r="194" customHeight="1" spans="1:1">
+      <c r="G193">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" spans="1:7">
       <c r="A194" s="3">
         <v>46151</v>
       </c>
-    </row>
-    <row r="195" customHeight="1" spans="1:1">
+      <c r="G194">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" spans="1:7">
       <c r="A195" s="3">
         <v>46152</v>
       </c>
-    </row>
-    <row r="196" customHeight="1" spans="1:1">
+      <c r="G195">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" spans="1:7">
       <c r="A196" s="3">
         <v>46153</v>
       </c>
-    </row>
-    <row r="197" customHeight="1" spans="1:1">
+      <c r="G196">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" spans="1:7">
       <c r="A197" s="3">
         <v>46154</v>
       </c>
-    </row>
-    <row r="198" customHeight="1" spans="1:1">
+      <c r="G197">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" spans="1:7">
       <c r="A198" s="3">
         <v>46155</v>
       </c>
-    </row>
-    <row r="199" customHeight="1" spans="1:1">
+      <c r="G198">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" spans="1:7">
       <c r="A199" s="3">
         <v>46156</v>
       </c>
-    </row>
-    <row r="200" customHeight="1" spans="1:1">
+      <c r="G199">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" spans="1:7">
       <c r="A200" s="3">
         <v>46157</v>
       </c>
-    </row>
-    <row r="201" customHeight="1" spans="1:1">
+      <c r="G200">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="1:7">
       <c r="A201" s="3">
         <v>46158</v>
       </c>
-    </row>
-    <row r="202" customHeight="1" spans="1:1">
+      <c r="G201">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="1:7">
       <c r="A202" s="3">
         <v>46159</v>
       </c>
-    </row>
-    <row r="203" customHeight="1" spans="1:1">
+      <c r="G202">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="1:7">
       <c r="A203" s="3">
         <v>46160</v>
       </c>
-    </row>
-    <row r="204" customHeight="1" spans="1:1">
+      <c r="G203">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="1:7">
       <c r="A204" s="3">
         <v>46161</v>
       </c>
-    </row>
-    <row r="205" customHeight="1" spans="1:1">
+      <c r="G204">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="1:7">
       <c r="A205" s="3">
         <v>46162</v>
       </c>
-    </row>
-    <row r="206" customHeight="1" spans="1:1">
+      <c r="G205">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="1:7">
       <c r="A206" s="3">
         <v>46163</v>
       </c>
-    </row>
-    <row r="207" customHeight="1" spans="1:1">
+      <c r="G206">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="1:7">
       <c r="A207" s="3">
         <v>46164</v>
       </c>
-    </row>
-    <row r="208" customHeight="1" spans="1:1">
+      <c r="G207">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="1:7">
       <c r="A208" s="3">
         <v>46165</v>
       </c>
-    </row>
-    <row r="209" customHeight="1" spans="1:1">
+      <c r="G208">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="1:7">
       <c r="A209" s="3">
         <v>46166</v>
       </c>
-    </row>
-    <row r="210" customHeight="1" spans="1:1">
+      <c r="G209">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="1:7">
       <c r="A210" s="3">
         <v>46167</v>
       </c>
-    </row>
-    <row r="211" customHeight="1" spans="1:1">
+      <c r="G210">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" spans="1:7">
       <c r="A211" s="3">
         <v>46168</v>
       </c>
-    </row>
-    <row r="212" customHeight="1" spans="1:1">
+      <c r="G211">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" spans="1:7">
       <c r="A212" s="3">
         <v>46169</v>
       </c>
-    </row>
-    <row r="213" customHeight="1" spans="1:1">
+      <c r="G212">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" spans="1:7">
       <c r="A213" s="3">
         <v>46170</v>
       </c>
-    </row>
-    <row r="214" customHeight="1" spans="1:1">
+      <c r="G213">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" spans="1:7">
       <c r="A214" s="3">
         <v>46171</v>
       </c>
-    </row>
-    <row r="215" customHeight="1" spans="1:1">
+      <c r="G214">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" spans="1:7">
       <c r="A215" s="3">
         <v>46172</v>
       </c>
-    </row>
-    <row r="216" customHeight="1" spans="1:1">
+      <c r="G215">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" spans="1:7">
       <c r="A216" s="3">
         <v>46173</v>
       </c>
-    </row>
-    <row r="217" customHeight="1" spans="1:1">
+      <c r="G216">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" spans="1:7">
       <c r="A217" s="3">
         <v>46174</v>
       </c>
-    </row>
-    <row r="218" customHeight="1" spans="1:1">
+      <c r="G217">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" spans="1:7">
       <c r="A218" s="3">
         <v>46175</v>
       </c>
-    </row>
-    <row r="219" customHeight="1" spans="1:1">
+      <c r="G218">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" spans="1:7">
       <c r="A219" s="3">
         <v>46176</v>
       </c>
-    </row>
-    <row r="220" customHeight="1" spans="1:1">
+      <c r="G219">
+        <f t="shared" ref="G219:G250" si="11">F219</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" spans="1:7">
       <c r="A220" s="3">
         <v>46177</v>
       </c>
-    </row>
-    <row r="221" customHeight="1" spans="1:1">
+      <c r="G220">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" spans="1:7">
       <c r="A221" s="3">
         <v>46178</v>
       </c>
-    </row>
-    <row r="222" customHeight="1" spans="1:1">
+      <c r="G221">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" spans="1:7">
       <c r="A222" s="3">
         <v>46179</v>
       </c>
-    </row>
-    <row r="223" customHeight="1" spans="1:1">
+      <c r="G222">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" spans="1:7">
       <c r="A223" s="3">
         <v>46180</v>
       </c>
-    </row>
-    <row r="224" customHeight="1" spans="1:1">
+      <c r="G223">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" spans="1:7">
       <c r="A224" s="3">
         <v>46181</v>
       </c>
-    </row>
-    <row r="225" customHeight="1" spans="1:1">
+      <c r="G224">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" spans="1:7">
       <c r="A225" s="3">
         <v>46182</v>
       </c>
-    </row>
-    <row r="226" customHeight="1" spans="1:1">
+      <c r="G225">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" spans="1:7">
       <c r="A226" s="3">
         <v>46183</v>
       </c>
-    </row>
-    <row r="227" customHeight="1" spans="1:1">
+      <c r="G226">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" spans="1:7">
       <c r="A227" s="3">
         <v>46184</v>
       </c>
-    </row>
-    <row r="228" customHeight="1" spans="1:1">
+      <c r="G227">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" spans="1:7">
       <c r="A228" s="3">
         <v>46185</v>
       </c>
-    </row>
-    <row r="229" customHeight="1" spans="1:1">
+      <c r="G228">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" spans="1:7">
       <c r="A229" s="3">
         <v>46186</v>
       </c>
-    </row>
-    <row r="230" customHeight="1" spans="1:1">
+      <c r="G229">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" spans="1:7">
       <c r="A230" s="3">
         <v>46187</v>
       </c>
-    </row>
-    <row r="231" customHeight="1" spans="1:1">
+      <c r="G230">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" spans="1:7">
       <c r="A231" s="3">
         <v>46188</v>
       </c>
-    </row>
-    <row r="232" customHeight="1" spans="1:1">
+      <c r="G231">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" spans="1:7">
       <c r="A232" s="3">
         <v>46189</v>
       </c>
-    </row>
-    <row r="233" customHeight="1" spans="1:1">
+      <c r="G232">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" spans="1:7">
       <c r="A233" s="3">
         <v>46190</v>
       </c>
-    </row>
-    <row r="234" customHeight="1" spans="1:1">
+      <c r="G233">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" spans="1:7">
       <c r="A234" s="3">
         <v>46191</v>
       </c>
-    </row>
-    <row r="235" customHeight="1" spans="1:1">
+      <c r="G234">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" spans="1:7">
       <c r="A235" s="3">
         <v>46192</v>
       </c>
-    </row>
-    <row r="236" customHeight="1" spans="1:1">
+      <c r="G235">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" spans="1:7">
       <c r="A236" s="3">
         <v>46193</v>
       </c>
-    </row>
-    <row r="237" customHeight="1" spans="1:1">
+      <c r="G236">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" spans="1:7">
       <c r="A237" s="3">
         <v>46194</v>
       </c>
-    </row>
-    <row r="238" customHeight="1" spans="1:1">
+      <c r="G237">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" spans="1:7">
       <c r="A238" s="3">
         <v>46195</v>
       </c>
-    </row>
-    <row r="239" customHeight="1" spans="1:1">
+      <c r="G238">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" spans="1:7">
       <c r="A239" s="3">
         <v>46196</v>
       </c>
-    </row>
-    <row r="240" customHeight="1" spans="1:1">
+      <c r="G239">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" spans="1:7">
       <c r="A240" s="3">
         <v>46197</v>
       </c>
-    </row>
-    <row r="241" customHeight="1" spans="1:1">
+      <c r="G240">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" spans="1:7">
       <c r="A241" s="3">
         <v>46198</v>
       </c>
-    </row>
-    <row r="242" customHeight="1" spans="1:1">
+      <c r="G241">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" customHeight="1" spans="1:7">
       <c r="A242" s="3">
         <v>46199</v>
       </c>
-    </row>
-    <row r="243" customHeight="1" spans="1:1">
+      <c r="G242">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" spans="1:7">
       <c r="A243" s="3">
         <v>46200</v>
       </c>
-    </row>
-    <row r="244" customHeight="1" spans="1:1">
+      <c r="G243">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" spans="1:7">
       <c r="A244" s="3">
         <v>46201</v>
       </c>
-    </row>
-    <row r="245" customHeight="1" spans="1:1">
+      <c r="G244">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" spans="1:7">
       <c r="A245" s="3">
         <v>46202</v>
       </c>
-    </row>
-    <row r="246" customHeight="1" spans="1:1">
+      <c r="G245">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" spans="1:7">
       <c r="A246" s="3">
         <v>46203</v>
       </c>
-    </row>
-    <row r="247" customHeight="1" spans="1:1">
+      <c r="G246">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" spans="1:7">
       <c r="A247" s="3">
         <v>46204</v>
       </c>
-    </row>
-    <row r="248" customHeight="1" spans="1:1">
+      <c r="G247">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" spans="1:7">
       <c r="A248" s="3">
         <v>46205</v>
       </c>
-    </row>
-    <row r="249" customHeight="1" spans="1:1">
+      <c r="G248">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" spans="1:7">
       <c r="A249" s="3">
         <v>46206</v>
       </c>
-    </row>
-    <row r="250" customHeight="1" spans="1:1">
+      <c r="G249">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" spans="1:7">
       <c r="A250" s="3">
         <v>46207</v>
       </c>
-    </row>
-    <row r="251" customHeight="1" spans="1:1">
+      <c r="G250">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" customHeight="1" spans="1:7">
       <c r="A251" s="3">
         <v>46208</v>
       </c>
-    </row>
-    <row r="252" customHeight="1" spans="1:1">
+      <c r="G251">
+        <f t="shared" ref="G251:G282" si="12">F251</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" customHeight="1" spans="1:7">
       <c r="A252" s="3">
         <v>46209</v>
       </c>
-    </row>
-    <row r="253" customHeight="1" spans="1:1">
+      <c r="G252">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" customHeight="1" spans="1:7">
       <c r="A253" s="3">
         <v>46210</v>
       </c>
-    </row>
-    <row r="254" customHeight="1" spans="1:1">
+      <c r="G253">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" customHeight="1" spans="1:7">
       <c r="A254" s="3">
         <v>46211</v>
       </c>
-    </row>
-    <row r="255" customHeight="1" spans="1:1">
+      <c r="G254">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" customHeight="1" spans="1:7">
       <c r="A255" s="3">
         <v>46212</v>
       </c>
-    </row>
-    <row r="256" customHeight="1" spans="1:1">
+      <c r="G255">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" spans="1:7">
       <c r="A256" s="3">
         <v>46213</v>
       </c>
-    </row>
-    <row r="257" customHeight="1" spans="1:1">
+      <c r="G256">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" spans="1:7">
       <c r="A257" s="3">
         <v>46214</v>
       </c>
-    </row>
-    <row r="258" customHeight="1" spans="1:1">
+      <c r="G257">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" spans="1:7">
       <c r="A258" s="3">
         <v>46215</v>
       </c>
-    </row>
-    <row r="259" customHeight="1" spans="1:1">
+      <c r="G258">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" spans="1:7">
       <c r="A259" s="3">
         <v>46216</v>
       </c>
-    </row>
-    <row r="260" customHeight="1" spans="1:1">
+      <c r="G259">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" spans="1:7">
       <c r="A260" s="3">
         <v>46217</v>
       </c>
-    </row>
-    <row r="261" customHeight="1" spans="1:1">
+      <c r="G260">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" spans="1:7">
       <c r="A261" s="3">
         <v>46218</v>
       </c>
-    </row>
-    <row r="262" customHeight="1" spans="1:1">
+      <c r="G261">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" spans="1:7">
       <c r="A262" s="3">
         <v>46219</v>
       </c>
-    </row>
-    <row r="263" customHeight="1" spans="1:1">
+      <c r="G262">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" spans="1:7">
       <c r="A263" s="3">
         <v>46220</v>
       </c>
-    </row>
-    <row r="264" customHeight="1" spans="1:1">
+      <c r="G263">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" spans="1:7">
       <c r="A264" s="3">
         <v>46221</v>
       </c>
-    </row>
-    <row r="265" customHeight="1" spans="1:1">
+      <c r="G264">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" spans="1:7">
       <c r="A265" s="3">
         <v>46222</v>
       </c>
-    </row>
-    <row r="266" customHeight="1" spans="1:1">
+      <c r="G265">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" spans="1:7">
       <c r="A266" s="3">
         <v>46223</v>
       </c>
-    </row>
-    <row r="267" customHeight="1" spans="1:1">
+      <c r="G266">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" customHeight="1" spans="1:7">
       <c r="A267" s="3">
         <v>46224</v>
       </c>
-    </row>
-    <row r="268" customHeight="1" spans="1:1">
+      <c r="G267">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" customHeight="1" spans="1:7">
       <c r="A268" s="3">
         <v>46225</v>
       </c>
-    </row>
-    <row r="269" customHeight="1" spans="1:1">
+      <c r="G268">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" customHeight="1" spans="1:7">
       <c r="A269" s="3">
         <v>46226</v>
       </c>
-    </row>
-    <row r="270" customHeight="1" spans="1:1">
+      <c r="G269">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" customHeight="1" spans="1:7">
       <c r="A270" s="3">
         <v>46227</v>
       </c>
-    </row>
-    <row r="271" customHeight="1" spans="1:1">
+      <c r="G270">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" customHeight="1" spans="1:7">
       <c r="A271" s="3">
         <v>46228</v>
       </c>
-    </row>
-    <row r="272" customHeight="1" spans="1:1">
+      <c r="G271">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" customHeight="1" spans="1:7">
       <c r="A272" s="3">
         <v>46229</v>
       </c>
-    </row>
-    <row r="273" customHeight="1" spans="1:1">
+      <c r="G272">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" customHeight="1" spans="1:7">
       <c r="A273" s="3">
         <v>46230</v>
       </c>
-    </row>
-    <row r="274" customHeight="1" spans="1:1">
+      <c r="G273">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" customHeight="1" spans="1:7">
       <c r="A274" s="3">
         <v>46231</v>
       </c>
-    </row>
-    <row r="275" customHeight="1" spans="1:1">
+      <c r="G274">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" customHeight="1" spans="1:7">
       <c r="A275" s="3">
         <v>46232</v>
       </c>
-    </row>
-    <row r="276" customHeight="1" spans="1:1">
+      <c r="G275">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" spans="1:7">
       <c r="A276" s="3">
         <v>46233</v>
       </c>
-    </row>
-    <row r="277" customHeight="1" spans="1:1">
+      <c r="G276">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" customHeight="1" spans="1:7">
       <c r="A277" s="3">
         <v>46234</v>
       </c>
-    </row>
-    <row r="278" customHeight="1" spans="1:1">
+      <c r="G277">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" customHeight="1" spans="1:7">
       <c r="A278" s="3">
         <v>46235</v>
       </c>
-    </row>
-    <row r="279" customHeight="1" spans="1:1">
+      <c r="G278">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" customHeight="1" spans="1:7">
       <c r="A279" s="3">
         <v>46236</v>
       </c>
-    </row>
-    <row r="280" customHeight="1" spans="1:1">
+      <c r="G279">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" customHeight="1" spans="1:7">
       <c r="A280" s="3">
         <v>46237</v>
       </c>
-    </row>
-    <row r="281" customHeight="1" spans="1:1">
+      <c r="G280">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" spans="1:7">
       <c r="A281" s="3">
         <v>46238</v>
       </c>
-    </row>
-    <row r="282" customHeight="1" spans="1:1">
+      <c r="G281">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" spans="1:7">
       <c r="A282" s="3">
         <v>46239</v>
       </c>
-    </row>
-    <row r="283" customHeight="1" spans="1:1">
+      <c r="G282">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" customHeight="1" spans="1:7">
       <c r="A283" s="3">
         <v>46240</v>
       </c>
-    </row>
-    <row r="284" customHeight="1" spans="1:1">
+      <c r="G283">
+        <f t="shared" ref="G283:G314" si="13">F283</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" spans="1:7">
       <c r="A284" s="3">
         <v>46241</v>
       </c>
-    </row>
-    <row r="285" customHeight="1" spans="1:1">
+      <c r="G284">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" customHeight="1" spans="1:7">
       <c r="A285" s="3">
         <v>46242</v>
       </c>
-    </row>
-    <row r="286" customHeight="1" spans="1:1">
+      <c r="G285">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" customHeight="1" spans="1:7">
       <c r="A286" s="3">
         <v>46243</v>
       </c>
-    </row>
-    <row r="287" customHeight="1" spans="1:1">
+      <c r="G286">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" customHeight="1" spans="1:7">
       <c r="A287" s="3">
         <v>46244</v>
       </c>
-    </row>
-    <row r="288" customHeight="1" spans="1:1">
+      <c r="G287">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" customHeight="1" spans="1:7">
       <c r="A288" s="3">
         <v>46245</v>
       </c>
-    </row>
-    <row r="289" customHeight="1" spans="1:1">
+      <c r="G288">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" customHeight="1" spans="1:7">
       <c r="A289" s="3">
         <v>46246</v>
       </c>
-    </row>
-    <row r="290" customHeight="1" spans="1:1">
+      <c r="G289">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" customHeight="1" spans="1:7">
       <c r="A290" s="3">
         <v>46247</v>
       </c>
-    </row>
-    <row r="291" customHeight="1" spans="1:1">
+      <c r="G290">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" customHeight="1" spans="1:7">
       <c r="A291" s="3">
         <v>46248</v>
       </c>
-    </row>
-    <row r="292" customHeight="1" spans="1:1">
+      <c r="G291">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" customHeight="1" spans="1:7">
       <c r="A292" s="3">
         <v>46249</v>
       </c>
-    </row>
-    <row r="293" customHeight="1" spans="1:1">
+      <c r="G292">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" customHeight="1" spans="1:7">
       <c r="A293" s="3">
         <v>46250</v>
       </c>
-    </row>
-    <row r="294" customHeight="1" spans="1:1">
+      <c r="G293">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" customHeight="1" spans="1:7">
       <c r="A294" s="3">
         <v>46251</v>
       </c>
-    </row>
-    <row r="295" customHeight="1" spans="1:1">
+      <c r="G294">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" customHeight="1" spans="1:7">
       <c r="A295" s="3">
         <v>46252</v>
       </c>
-    </row>
-    <row r="296" customHeight="1" spans="1:1">
+      <c r="G295">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" customHeight="1" spans="1:7">
       <c r="A296" s="3">
         <v>46253</v>
       </c>
-    </row>
-    <row r="297" customHeight="1" spans="1:1">
+      <c r="G296">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" customHeight="1" spans="1:7">
       <c r="A297" s="3">
         <v>46254</v>
       </c>
-    </row>
-    <row r="298" customHeight="1" spans="1:1">
+      <c r="G297">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" customHeight="1" spans="1:7">
       <c r="A298" s="3">
         <v>46255</v>
       </c>
-    </row>
-    <row r="299" customHeight="1" spans="1:1">
+      <c r="G298">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" customHeight="1" spans="1:7">
       <c r="A299" s="3">
         <v>46256</v>
       </c>
-    </row>
-    <row r="300" customHeight="1" spans="1:1">
+      <c r="G299">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" customHeight="1" spans="1:7">
       <c r="A300" s="3">
         <v>46257</v>
       </c>
-    </row>
-    <row r="301" customHeight="1" spans="1:1">
+      <c r="G300">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" customHeight="1" spans="1:7">
       <c r="A301" s="3">
         <v>46258</v>
       </c>
-    </row>
-    <row r="302" customHeight="1" spans="1:1">
+      <c r="G301">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" customHeight="1" spans="1:7">
       <c r="A302" s="3">
         <v>46259</v>
       </c>
-    </row>
-    <row r="303" customHeight="1" spans="1:1">
+      <c r="G302">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" customHeight="1" spans="1:7">
       <c r="A303" s="3">
         <v>46260</v>
       </c>
-    </row>
-    <row r="304" customHeight="1" spans="1:1">
+      <c r="G303">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" customHeight="1" spans="1:7">
       <c r="A304" s="3">
         <v>46261</v>
       </c>
-    </row>
-    <row r="305" customHeight="1" spans="1:1">
+      <c r="G304">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" customHeight="1" spans="1:7">
       <c r="A305" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="306" customHeight="1" spans="1:1">
+      <c r="G305">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" customHeight="1" spans="1:7">
       <c r="A306" s="3">
         <v>46263</v>
       </c>
-    </row>
-    <row r="307" customHeight="1" spans="1:1">
+      <c r="G306">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" customHeight="1" spans="1:7">
       <c r="A307" s="3">
         <v>46264</v>
       </c>
-    </row>
-    <row r="308" customHeight="1" spans="1:1">
+      <c r="G307">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" customHeight="1" spans="1:7">
       <c r="A308" s="3">
         <v>46265</v>
       </c>
-    </row>
-    <row r="309" customHeight="1" spans="1:1">
+      <c r="G308">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" customHeight="1" spans="1:7">
       <c r="A309" s="3">
         <v>46266</v>
       </c>
-    </row>
-    <row r="310" customHeight="1" spans="1:1">
+      <c r="G309">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" customHeight="1" spans="1:7">
       <c r="A310" s="3">
         <v>46267</v>
       </c>
-    </row>
-    <row r="311" customHeight="1" spans="1:1">
+      <c r="G310">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" customHeight="1" spans="1:7">
       <c r="A311" s="3">
         <v>46268</v>
       </c>
-    </row>
-    <row r="312" customHeight="1" spans="1:1">
+      <c r="G311">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" customHeight="1" spans="1:7">
       <c r="A312" s="3">
         <v>46269</v>
       </c>
-    </row>
-    <row r="313" customHeight="1" spans="1:1">
+      <c r="G312">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" customHeight="1" spans="1:7">
       <c r="A313" s="3">
         <v>46270</v>
       </c>
-    </row>
-    <row r="314" customHeight="1" spans="1:1">
+      <c r="G313">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" spans="1:7">
       <c r="A314" s="3">
         <v>46271</v>
       </c>
-    </row>
-    <row r="315" customHeight="1" spans="1:1">
+      <c r="G314">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" spans="1:7">
       <c r="A315" s="3">
         <v>46272</v>
       </c>
-    </row>
-    <row r="316" customHeight="1" spans="1:1">
+      <c r="G315">
+        <f t="shared" ref="G315:G346" si="14">F315</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" spans="1:7">
       <c r="A316" s="3">
         <v>46273</v>
       </c>
-    </row>
-    <row r="317" customHeight="1" spans="1:1">
+      <c r="G316">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" customHeight="1" spans="1:7">
       <c r="A317" s="3">
         <v>46274</v>
       </c>
-    </row>
-    <row r="318" customHeight="1" spans="1:1">
+      <c r="G317">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" customHeight="1" spans="1:7">
       <c r="A318" s="3">
         <v>46275</v>
       </c>
-    </row>
-    <row r="319" customHeight="1" spans="1:1">
+      <c r="G318">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" customHeight="1" spans="1:7">
       <c r="A319" s="3">
         <v>46276</v>
       </c>
-    </row>
-    <row r="320" customHeight="1" spans="1:1">
+      <c r="G319">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" customHeight="1" spans="1:7">
       <c r="A320" s="3">
         <v>46277</v>
       </c>
-    </row>
-    <row r="321" customHeight="1" spans="1:1">
+      <c r="G320">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" customHeight="1" spans="1:7">
       <c r="A321" s="3">
         <v>46278</v>
       </c>
-    </row>
-    <row r="322" customHeight="1" spans="1:1">
+      <c r="G321">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" customHeight="1" spans="1:7">
       <c r="A322" s="3">
         <v>46279</v>
       </c>
-    </row>
-    <row r="323" customHeight="1" spans="1:1">
+      <c r="G322">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" customHeight="1" spans="1:7">
       <c r="A323" s="3">
         <v>46280</v>
       </c>
-    </row>
-    <row r="324" customHeight="1" spans="1:1">
+      <c r="G323">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" customHeight="1" spans="1:7">
       <c r="A324" s="3">
         <v>46281</v>
       </c>
-    </row>
-    <row r="325" customHeight="1" spans="1:1">
+      <c r="G324">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" customHeight="1" spans="1:7">
       <c r="A325" s="3">
         <v>46282</v>
       </c>
-    </row>
-    <row r="326" customHeight="1" spans="1:1">
+      <c r="G325">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" customHeight="1" spans="1:7">
       <c r="A326" s="3">
         <v>46283</v>
       </c>
-    </row>
-    <row r="327" customHeight="1" spans="1:1">
+      <c r="G326">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" customHeight="1" spans="1:7">
       <c r="A327" s="3">
         <v>46284</v>
       </c>
-    </row>
-    <row r="328" customHeight="1" spans="1:1">
+      <c r="G327">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" customHeight="1" spans="1:7">
       <c r="A328" s="3">
         <v>46285</v>
       </c>
-    </row>
-    <row r="329" customHeight="1" spans="1:1">
+      <c r="G328">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" customHeight="1" spans="1:7">
       <c r="A329" s="3">
         <v>46286</v>
       </c>
-    </row>
-    <row r="330" customHeight="1" spans="1:1">
+      <c r="G329">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" customHeight="1" spans="1:7">
       <c r="A330" s="3">
         <v>46287</v>
       </c>
-    </row>
-    <row r="331" customHeight="1" spans="1:1">
+      <c r="G330">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" customHeight="1" spans="1:7">
       <c r="A331" s="3">
         <v>46288</v>
       </c>
-    </row>
-    <row r="332" customHeight="1" spans="1:1">
+      <c r="G331">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" customHeight="1" spans="1:7">
       <c r="A332" s="3">
         <v>46289</v>
       </c>
-    </row>
-    <row r="333" customHeight="1" spans="1:1">
+      <c r="G332">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" customHeight="1" spans="1:7">
       <c r="A333" s="3">
         <v>46290</v>
       </c>
-    </row>
-    <row r="334" customHeight="1" spans="1:1">
+      <c r="G333">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" customHeight="1" spans="1:7">
       <c r="A334" s="3">
         <v>46291</v>
       </c>
-    </row>
-    <row r="335" customHeight="1" spans="1:1">
+      <c r="G334">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" customHeight="1" spans="1:7">
       <c r="A335" s="3">
         <v>46292</v>
       </c>
-    </row>
-    <row r="336" customHeight="1" spans="1:1">
+      <c r="G335">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" customHeight="1" spans="1:7">
       <c r="A336" s="3">
         <v>46293</v>
       </c>
-    </row>
-    <row r="337" customHeight="1" spans="1:1">
+      <c r="G336">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" customHeight="1" spans="1:7">
       <c r="A337" s="3">
         <v>46294</v>
       </c>
-    </row>
-    <row r="338" customHeight="1" spans="1:1">
+      <c r="G337">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" customHeight="1" spans="1:7">
       <c r="A338" s="3">
         <v>46295</v>
       </c>
-    </row>
-    <row r="339" customHeight="1" spans="1:1">
+      <c r="G338">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" customHeight="1" spans="1:7">
       <c r="A339" s="3">
         <v>46296</v>
       </c>
-    </row>
-    <row r="340" customHeight="1" spans="1:1">
+      <c r="G339">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" customHeight="1" spans="1:7">
       <c r="A340" s="3">
         <v>46297</v>
       </c>
-    </row>
-    <row r="341" customHeight="1" spans="1:1">
+      <c r="G340">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" customHeight="1" spans="1:7">
       <c r="A341" s="3">
         <v>46298</v>
       </c>
-    </row>
-    <row r="342" customHeight="1" spans="1:1">
+      <c r="G341">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" customHeight="1" spans="1:7">
       <c r="A342" s="3">
         <v>46299</v>
       </c>
-    </row>
-    <row r="343" customHeight="1" spans="1:1">
+      <c r="G342">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" customHeight="1" spans="1:7">
       <c r="A343" s="3">
         <v>46300</v>
       </c>
-    </row>
-    <row r="344" customHeight="1" spans="1:1">
+      <c r="G343">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" customHeight="1" spans="1:7">
       <c r="A344" s="3">
         <v>46301</v>
       </c>
-    </row>
-    <row r="345" customHeight="1" spans="1:1">
+      <c r="G344">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" customHeight="1" spans="1:7">
       <c r="A345" s="3">
         <v>46302</v>
       </c>
-    </row>
-    <row r="346" customHeight="1" spans="1:1">
+      <c r="G345">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" customHeight="1" spans="1:7">
       <c r="A346" s="3">
         <v>46303</v>
       </c>
-    </row>
-    <row r="347" customHeight="1" spans="1:1">
+      <c r="G346">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" customHeight="1" spans="1:7">
       <c r="A347" s="3">
         <v>46304</v>
       </c>
-    </row>
-    <row r="348" customHeight="1" spans="1:1">
+      <c r="G347">
+        <f>F347</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" customHeight="1" spans="1:7">
       <c r="A348" s="3">
         <v>46305</v>
       </c>
-    </row>
-    <row r="349" customHeight="1" spans="1:1">
+      <c r="G348">
+        <f>F348</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" customHeight="1" spans="1:7">
       <c r="A349" s="3">
         <v>46306</v>
       </c>
-    </row>
-    <row r="350" customHeight="1" spans="1:1">
+      <c r="G349">
+        <f>F349</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" customHeight="1" spans="1:7">
       <c r="A350" s="3">
         <v>46307</v>
       </c>
-    </row>
-    <row r="351" customHeight="1" spans="1:1">
+      <c r="G350">
+        <f>F350</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" customHeight="1" spans="1:7">
       <c r="A351" s="3">
         <v>46308</v>
       </c>
-    </row>
-    <row r="352" customHeight="1" spans="1:1">
+      <c r="G351">
+        <f>F351</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" customHeight="1" spans="1:7">
       <c r="A352" s="3">
         <v>46309</v>
+      </c>
+      <c r="G352">
+        <f>F352</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1211,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J194"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1"/>
@@ -4464,17 +4464,65 @@
       <c r="A100" s="2">
         <v>46059</v>
       </c>
+      <c r="B100" s="1">
+        <v>5305</v>
+      </c>
+      <c r="C100" s="1">
+        <v>4950</v>
+      </c>
       <c r="D100" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>355</v>
+      </c>
+      <c r="E100" s="1">
+        <v>90</v>
+      </c>
+      <c r="F100" s="1">
+        <v>5</v>
+      </c>
+      <c r="G100" s="1">
+        <v>5</v>
+      </c>
+      <c r="H100" s="1">
+        <v>232</v>
+      </c>
+      <c r="I100" s="1">
+        <v>17</v>
+      </c>
+      <c r="J100" s="1">
+        <v>314</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:10">
       <c r="A101" s="2">
         <v>46060</v>
       </c>
+      <c r="B101" s="1">
+        <v>4100</v>
+      </c>
+      <c r="C101" s="1">
+        <v>3822</v>
+      </c>
       <c r="D101" s="1">
         <f t="shared" si="4"/>
+        <v>278</v>
+      </c>
+      <c r="E101" s="1">
+        <v>114</v>
+      </c>
+      <c r="F101" s="1">
+        <v>1</v>
+      </c>
+      <c r="G101" s="1">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1">
+        <v>155</v>
+      </c>
+      <c r="I101" s="1">
+        <v>1</v>
+      </c>
+      <c r="J101" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4482,17 +4530,65 @@
       <c r="A102" s="2">
         <v>46061</v>
       </c>
+      <c r="B102" s="1">
+        <v>292</v>
+      </c>
+      <c r="C102" s="1">
+        <v>115</v>
+      </c>
       <c r="D102" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>177</v>
+      </c>
+      <c r="E102" s="1">
+        <v>7</v>
+      </c>
+      <c r="F102" s="1">
+        <v>2</v>
+      </c>
+      <c r="G102" s="1">
+        <v>2</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1">
+        <v>2348</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:10">
       <c r="A103" s="2">
         <v>46062</v>
       </c>
+      <c r="B103" s="1">
+        <v>2087</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1820</v>
+      </c>
       <c r="D103" s="1">
         <f t="shared" si="4"/>
+        <v>267</v>
+      </c>
+      <c r="E103" s="1">
+        <v>23</v>
+      </c>
+      <c r="F103" s="1">
+        <v>1</v>
+      </c>
+      <c r="G103" s="1">
+        <v>2</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4500,35 +4596,135 @@
       <c r="A104" s="2">
         <v>46063</v>
       </c>
+      <c r="B104" s="1">
+        <v>289</v>
+      </c>
+      <c r="C104" s="1">
+        <v>110</v>
+      </c>
       <c r="D104" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>179</v>
+      </c>
+      <c r="E104" s="1">
+        <v>7</v>
+      </c>
+      <c r="F104" s="1">
+        <v>1</v>
+      </c>
+      <c r="G104" s="1">
+        <f>F104</f>
+        <v>1</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+      <c r="I104" s="1">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1">
+        <v>600</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:10">
       <c r="A105" s="2">
         <v>46064</v>
       </c>
+      <c r="B105" s="1">
+        <v>333</v>
+      </c>
+      <c r="C105" s="1">
+        <v>150</v>
+      </c>
       <c r="D105" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>183</v>
+      </c>
+      <c r="E105" s="1">
+        <v>12</v>
+      </c>
+      <c r="F105" s="1">
+        <v>1</v>
+      </c>
+      <c r="G105" s="1">
+        <f t="shared" ref="G105:G136" si="5">F105</f>
+        <v>1</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:10">
       <c r="A106" s="2">
         <v>46065</v>
       </c>
+      <c r="B106" s="1">
+        <v>293</v>
+      </c>
+      <c r="C106" s="1">
+        <v>137</v>
+      </c>
       <c r="D106" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>156</v>
+      </c>
+      <c r="E106" s="1">
+        <v>9</v>
+      </c>
+      <c r="F106" s="1">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1">
+        <v>0</v>
+      </c>
+      <c r="J106" s="1">
+        <v>61</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:10">
       <c r="A107" s="2">
         <v>46066</v>
       </c>
+      <c r="B107" s="1">
+        <v>221</v>
+      </c>
+      <c r="C107" s="1">
+        <v>123</v>
+      </c>
       <c r="D107" s="1">
         <f t="shared" si="4"/>
+        <v>98</v>
+      </c>
+      <c r="E107" s="1">
+        <v>4</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1">
+        <v>0</v>
+      </c>
+      <c r="J107" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4536,8 +4732,33 @@
       <c r="A108" s="2">
         <v>46067</v>
       </c>
+      <c r="B108" s="1">
+        <v>162</v>
+      </c>
+      <c r="C108" s="1">
+        <v>108</v>
+      </c>
       <c r="D108" s="1">
         <f t="shared" si="4"/>
+        <v>54</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="1">
+        <v>0</v>
+      </c>
+      <c r="G108" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
+      <c r="I108" s="1">
+        <v>0</v>
+      </c>
+      <c r="J108" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4545,8 +4766,33 @@
       <c r="A109" s="2">
         <v>46068</v>
       </c>
+      <c r="B109" s="1">
+        <v>172</v>
+      </c>
+      <c r="C109" s="1">
+        <v>103</v>
+      </c>
       <c r="D109" s="1">
         <f t="shared" si="4"/>
+        <v>69</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="1">
+        <v>0</v>
+      </c>
+      <c r="G109" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H109" s="1">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1">
+        <v>0</v>
+      </c>
+      <c r="J109" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4554,8 +4800,33 @@
       <c r="A110" s="2">
         <v>46069</v>
       </c>
+      <c r="B110" s="1">
+        <v>186</v>
+      </c>
+      <c r="C110" s="1">
+        <v>99</v>
+      </c>
       <c r="D110" s="1">
         <f t="shared" si="4"/>
+        <v>87</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="1">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
+      </c>
+      <c r="I110" s="1">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4563,8 +4834,33 @@
       <c r="A111" s="2">
         <v>46070</v>
       </c>
+      <c r="B111" s="1">
+        <v>183</v>
+      </c>
+      <c r="C111" s="1">
+        <v>110</v>
+      </c>
       <c r="D111" s="1">
         <f t="shared" si="4"/>
+        <v>73</v>
+      </c>
+      <c r="E111" s="1">
+        <v>2</v>
+      </c>
+      <c r="F111" s="1">
+        <v>0</v>
+      </c>
+      <c r="G111" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H111" s="1">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1">
+        <v>0</v>
+      </c>
+      <c r="J111" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4572,494 +4868,2495 @@
       <c r="A112" s="2">
         <v>46071</v>
       </c>
+      <c r="B112" s="1">
+        <v>176</v>
+      </c>
+      <c r="C112" s="1">
+        <v>108</v>
+      </c>
       <c r="D112" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="1:4">
+        <v>68</v>
+      </c>
+      <c r="E112" s="1">
+        <v>1</v>
+      </c>
+      <c r="F112" s="1">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+      <c r="I112" s="1">
+        <v>0</v>
+      </c>
+      <c r="J112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:10">
       <c r="A113" s="2">
         <v>46072</v>
       </c>
+      <c r="B113" s="1">
+        <v>147</v>
+      </c>
+      <c r="C113" s="1">
+        <v>96</v>
+      </c>
       <c r="D113" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" spans="1:4">
+        <v>51</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0</v>
+      </c>
+      <c r="F113" s="1">
+        <v>0</v>
+      </c>
+      <c r="G113" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+      <c r="I113" s="1">
+        <v>0</v>
+      </c>
+      <c r="J113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="1:10">
       <c r="A114" s="2">
         <v>46073</v>
       </c>
+      <c r="B114" s="1">
+        <v>162</v>
+      </c>
+      <c r="C114" s="1">
+        <v>99</v>
+      </c>
       <c r="D114" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" spans="1:4">
+        <v>63</v>
+      </c>
+      <c r="E114" s="1">
+        <v>5</v>
+      </c>
+      <c r="F114" s="1">
+        <v>2</v>
+      </c>
+      <c r="G114" s="1">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H114" s="1">
+        <v>0</v>
+      </c>
+      <c r="I114" s="1">
+        <v>0</v>
+      </c>
+      <c r="J114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="1:10">
       <c r="A115" s="2">
         <v>46074</v>
       </c>
+      <c r="B115" s="1">
+        <v>364</v>
+      </c>
+      <c r="C115" s="1">
+        <v>107</v>
+      </c>
       <c r="D115" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" spans="1:4">
+        <v>257</v>
+      </c>
+      <c r="E115" s="1">
+        <v>5</v>
+      </c>
+      <c r="F115" s="1">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H115" s="1">
+        <v>0</v>
+      </c>
+      <c r="I115" s="1">
+        <v>0</v>
+      </c>
+      <c r="J115" s="1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="1:10">
       <c r="A116" s="2">
         <v>46075</v>
       </c>
+      <c r="B116" s="1">
+        <v>251</v>
+      </c>
+      <c r="C116" s="1">
+        <v>108</v>
+      </c>
       <c r="D116" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="1:4">
+        <v>143</v>
+      </c>
+      <c r="E116" s="1">
+        <v>3</v>
+      </c>
+      <c r="F116" s="1">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+      <c r="I116" s="1">
+        <v>0</v>
+      </c>
+      <c r="J116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="1:10">
       <c r="A117" s="2">
         <v>46076</v>
       </c>
+      <c r="B117" s="1">
+        <v>269</v>
+      </c>
+      <c r="C117" s="1">
+        <v>111</v>
+      </c>
       <c r="D117" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" spans="1:4">
+        <v>158</v>
+      </c>
+      <c r="E117" s="1">
+        <v>4</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="1:10">
       <c r="A118" s="2">
         <v>46077</v>
       </c>
+      <c r="B118" s="1">
+        <v>2436</v>
+      </c>
+      <c r="C118" s="1">
+        <v>2151</v>
+      </c>
       <c r="D118" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" spans="1:4">
+        <v>285</v>
+      </c>
+      <c r="E118" s="1">
+        <v>74</v>
+      </c>
+      <c r="F118" s="1">
+        <v>5</v>
+      </c>
+      <c r="G118" s="1">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H118" s="1">
+        <v>83</v>
+      </c>
+      <c r="I118" s="1">
+        <v>4</v>
+      </c>
+      <c r="J118" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="1:10">
       <c r="A119" s="2">
         <v>46078</v>
       </c>
+      <c r="B119" s="1">
+        <v>2758</v>
+      </c>
+      <c r="C119" s="1">
+        <v>2472</v>
+      </c>
       <c r="D119" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" spans="1:4">
+        <v>286</v>
+      </c>
+      <c r="E119" s="1">
+        <v>85</v>
+      </c>
+      <c r="F119" s="1">
+        <v>5</v>
+      </c>
+      <c r="G119" s="1">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H119" s="1">
+        <v>102</v>
+      </c>
+      <c r="I119" s="1">
+        <v>7</v>
+      </c>
+      <c r="J119" s="1">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="1:10">
       <c r="A120" s="2">
         <v>46079</v>
       </c>
+      <c r="B120" s="1">
+        <v>5015</v>
+      </c>
+      <c r="C120" s="1">
+        <v>4518</v>
+      </c>
       <c r="D120" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" spans="1:4">
+        <v>497</v>
+      </c>
+      <c r="E120" s="1">
+        <v>114</v>
+      </c>
+      <c r="F120" s="1">
+        <v>10</v>
+      </c>
+      <c r="G120" s="1">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="H120" s="1">
+        <v>224</v>
+      </c>
+      <c r="I120" s="1">
+        <v>12</v>
+      </c>
+      <c r="J120" s="1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="1:10">
       <c r="A121" s="2">
         <v>46080</v>
       </c>
+      <c r="B121" s="1">
+        <v>3881</v>
+      </c>
+      <c r="C121" s="1">
+        <v>3570</v>
+      </c>
       <c r="D121" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" customHeight="1" spans="1:4">
+        <v>311</v>
+      </c>
+      <c r="E121" s="1">
+        <v>112</v>
+      </c>
+      <c r="F121" s="1">
+        <v>4</v>
+      </c>
+      <c r="G121" s="1">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="H121" s="1">
+        <v>193</v>
+      </c>
+      <c r="I121" s="1">
+        <v>4</v>
+      </c>
+      <c r="J121" s="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="1:10">
       <c r="A122" s="2">
         <v>46081</v>
       </c>
+      <c r="B122" s="1">
+        <v>4112</v>
+      </c>
+      <c r="C122" s="1">
+        <v>3695</v>
+      </c>
       <c r="D122" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" spans="1:4">
+        <v>417</v>
+      </c>
+      <c r="E122" s="1">
+        <v>87</v>
+      </c>
+      <c r="F122" s="1">
+        <v>3</v>
+      </c>
+      <c r="G122" s="1">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H122" s="1">
+        <v>84</v>
+      </c>
+      <c r="I122" s="1">
+        <v>3</v>
+      </c>
+      <c r="J122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="1:10">
       <c r="A123" s="2">
         <v>46082</v>
       </c>
+      <c r="B123" s="1">
+        <v>251</v>
+      </c>
+      <c r="C123" s="1">
+        <v>52</v>
+      </c>
       <c r="D123" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" spans="1:4">
+        <v>199</v>
+      </c>
+      <c r="E123" s="1">
+        <v>14</v>
+      </c>
+      <c r="F123" s="1">
+        <v>2</v>
+      </c>
+      <c r="G123" s="1">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+      <c r="I123" s="1">
+        <v>0</v>
+      </c>
+      <c r="J123" s="1">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="1:10">
       <c r="A124" s="2">
         <v>46083</v>
       </c>
+      <c r="B124" s="1">
+        <v>5433</v>
+      </c>
+      <c r="C124" s="1">
+        <v>5062</v>
+      </c>
       <c r="D124" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" spans="1:4">
+        <v>371</v>
+      </c>
+      <c r="E124" s="1">
+        <v>140</v>
+      </c>
+      <c r="F124" s="1">
+        <v>3</v>
+      </c>
+      <c r="G124" s="1">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H124" s="1">
+        <v>208</v>
+      </c>
+      <c r="I124" s="1">
+        <v>4</v>
+      </c>
+      <c r="J124" s="1">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="1:10">
       <c r="A125" s="2">
         <v>46084</v>
       </c>
+      <c r="B125" s="1">
+        <v>4509</v>
+      </c>
+      <c r="C125" s="1">
+        <v>4173</v>
+      </c>
       <c r="D125" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" customHeight="1" spans="1:4">
+        <v>336</v>
+      </c>
+      <c r="E125" s="1">
+        <v>99</v>
+      </c>
+      <c r="F125" s="1">
+        <v>3</v>
+      </c>
+      <c r="G125" s="1">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="H125" s="1">
+        <v>211</v>
+      </c>
+      <c r="I125" s="1">
+        <v>8</v>
+      </c>
+      <c r="J125" s="1">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="1:10">
       <c r="A126" s="2">
         <v>46085</v>
       </c>
+      <c r="B126" s="1">
+        <v>3730</v>
+      </c>
+      <c r="C126" s="1">
+        <v>3412</v>
+      </c>
       <c r="D126" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" customHeight="1" spans="1:4">
+        <v>318</v>
+      </c>
+      <c r="E126" s="1">
+        <v>110</v>
+      </c>
+      <c r="F126" s="1">
+        <v>10</v>
+      </c>
+      <c r="G126" s="1">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="H126" s="1">
+        <v>223</v>
+      </c>
+      <c r="I126" s="1">
+        <v>4</v>
+      </c>
+      <c r="J126" s="1">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:10">
       <c r="A127" s="2">
         <v>46086</v>
       </c>
+      <c r="B127" s="1">
+        <v>6090</v>
+      </c>
+      <c r="C127" s="1">
+        <v>5782</v>
+      </c>
       <c r="D127" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" customHeight="1" spans="1:4">
+        <v>308</v>
+      </c>
+      <c r="E127" s="1">
+        <v>112</v>
+      </c>
+      <c r="F127" s="1">
+        <v>6</v>
+      </c>
+      <c r="G127" s="1">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H127" s="1">
+        <v>223</v>
+      </c>
+      <c r="I127" s="1">
+        <v>13</v>
+      </c>
+      <c r="J127" s="1">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:10">
       <c r="A128" s="2">
         <v>46087</v>
       </c>
+      <c r="B128" s="1">
+        <v>5546</v>
+      </c>
+      <c r="C128" s="1">
+        <v>5253</v>
+      </c>
       <c r="D128" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" spans="1:4">
+        <v>293</v>
+      </c>
+      <c r="E128" s="1">
+        <v>130</v>
+      </c>
+      <c r="F128" s="1">
+        <v>5</v>
+      </c>
+      <c r="G128" s="1">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H128" s="1">
+        <v>214</v>
+      </c>
+      <c r="I128" s="1">
+        <v>5</v>
+      </c>
+      <c r="J128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="1:10">
       <c r="A129" s="2">
         <v>46088</v>
       </c>
+      <c r="B129" s="1">
+        <v>3961</v>
+      </c>
+      <c r="C129" s="1">
+        <v>3657</v>
+      </c>
       <c r="D129" s="1">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" spans="1:4">
+        <v>304</v>
+      </c>
+      <c r="E129" s="1">
+        <v>102</v>
+      </c>
+      <c r="F129" s="1">
+        <v>4</v>
+      </c>
+      <c r="G129" s="1">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="H129" s="1">
+        <v>216</v>
+      </c>
+      <c r="I129" s="1">
+        <v>3</v>
+      </c>
+      <c r="J129" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="1:10">
       <c r="A130" s="2">
         <v>46089</v>
       </c>
+      <c r="B130" s="1">
+        <v>1652</v>
+      </c>
+      <c r="C130" s="1">
+        <v>1385</v>
+      </c>
       <c r="D130" s="1">
-        <f t="shared" ref="D130:D166" si="5">B130-C130</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" spans="1:4">
+        <f t="shared" ref="D130:D166" si="6">B130-C130</f>
+        <v>267</v>
+      </c>
+      <c r="E130" s="1">
+        <v>42</v>
+      </c>
+      <c r="F130" s="1">
+        <v>2</v>
+      </c>
+      <c r="G130" s="1">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H130" s="1">
+        <v>126</v>
+      </c>
+      <c r="I130" s="1">
+        <v>0</v>
+      </c>
+      <c r="J130" s="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="1:10">
       <c r="A131" s="2">
         <v>46090</v>
       </c>
+      <c r="B131" s="1">
+        <v>6885</v>
+      </c>
+      <c r="C131" s="1">
+        <v>6539</v>
+      </c>
       <c r="D131" s="1">
+        <f t="shared" si="6"/>
+        <v>346</v>
+      </c>
+      <c r="E131" s="1">
+        <v>129</v>
+      </c>
+      <c r="F131" s="1">
+        <v>3</v>
+      </c>
+      <c r="G131" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" customHeight="1" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="H131" s="1">
+        <v>225</v>
+      </c>
+      <c r="I131" s="1">
+        <v>2</v>
+      </c>
+      <c r="J131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="1:10">
       <c r="A132" s="2">
         <v>46091</v>
       </c>
+      <c r="B132" s="1">
+        <v>4708</v>
+      </c>
+      <c r="C132" s="1">
+        <v>4087</v>
+      </c>
       <c r="D132" s="1">
+        <f t="shared" si="6"/>
+        <v>621</v>
+      </c>
+      <c r="E132" s="1">
+        <v>95</v>
+      </c>
+      <c r="F132" s="1">
+        <v>4</v>
+      </c>
+      <c r="G132" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" customHeight="1" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="H132" s="1">
+        <v>210</v>
+      </c>
+      <c r="I132" s="1">
+        <v>3</v>
+      </c>
+      <c r="J132" s="1">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="1:10">
       <c r="A133" s="2">
         <v>46092</v>
       </c>
+      <c r="B133" s="1">
+        <v>5997</v>
+      </c>
+      <c r="C133" s="1">
+        <v>5633</v>
+      </c>
       <c r="D133" s="1">
+        <f t="shared" si="6"/>
+        <v>364</v>
+      </c>
+      <c r="E133" s="1">
+        <v>97</v>
+      </c>
+      <c r="F133" s="1">
+        <v>3</v>
+      </c>
+      <c r="G133" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="H133" s="1">
+        <v>205</v>
+      </c>
+      <c r="I133" s="1">
+        <v>10</v>
+      </c>
+      <c r="J133" s="1">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="1:10">
       <c r="A134" s="2">
         <v>46093</v>
       </c>
+      <c r="B134" s="1">
+        <v>5208</v>
+      </c>
+      <c r="C134" s="1">
+        <v>4874</v>
+      </c>
       <c r="D134" s="1">
+        <f t="shared" si="6"/>
+        <v>334</v>
+      </c>
+      <c r="E134" s="1">
+        <v>123</v>
+      </c>
+      <c r="F134" s="1">
+        <v>3</v>
+      </c>
+      <c r="G134" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" spans="1:4">
+        <v>3</v>
+      </c>
+      <c r="H134" s="1">
+        <v>230</v>
+      </c>
+      <c r="I134" s="1">
+        <v>2</v>
+      </c>
+      <c r="J134" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="1:10">
       <c r="A135" s="2">
         <v>46094</v>
       </c>
+      <c r="B135" s="1">
+        <v>5141</v>
+      </c>
+      <c r="C135" s="1">
+        <v>4778</v>
+      </c>
       <c r="D135" s="1">
+        <f t="shared" si="6"/>
+        <v>363</v>
+      </c>
+      <c r="E135" s="1">
+        <v>101</v>
+      </c>
+      <c r="F135" s="1">
+        <v>7</v>
+      </c>
+      <c r="G135" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" customHeight="1" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="H135" s="1">
+        <v>175</v>
+      </c>
+      <c r="I135" s="1">
+        <v>6</v>
+      </c>
+      <c r="J135" s="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="1:10">
       <c r="A136" s="2">
         <v>46095</v>
       </c>
+      <c r="B136" s="1">
+        <v>3678</v>
+      </c>
+      <c r="C136" s="1">
+        <v>3391</v>
+      </c>
       <c r="D136" s="1">
+        <f t="shared" si="6"/>
+        <v>287</v>
+      </c>
+      <c r="E136" s="1">
+        <v>85</v>
+      </c>
+      <c r="F136" s="1">
+        <v>7</v>
+      </c>
+      <c r="G136" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" customHeight="1" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="H136" s="1">
+        <v>86</v>
+      </c>
+      <c r="I136" s="1">
+        <v>2</v>
+      </c>
+      <c r="J136" s="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="1:10">
       <c r="A137" s="2">
         <v>46096</v>
       </c>
+      <c r="B137" s="1">
+        <v>444</v>
+      </c>
+      <c r="C137" s="1">
+        <v>156</v>
+      </c>
       <c r="D137" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>288</v>
+      </c>
+      <c r="E137" s="1">
+        <v>14</v>
+      </c>
+      <c r="F137" s="1">
+        <v>2</v>
+      </c>
+      <c r="G137" s="1">
+        <f t="shared" ref="G137:G166" si="7">F137</f>
+        <v>2</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+      <c r="I137" s="1">
+        <v>0</v>
+      </c>
+      <c r="J137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="1:10">
       <c r="A138" s="2">
         <v>46097</v>
       </c>
+      <c r="B138" s="1">
+        <v>4154</v>
+      </c>
+      <c r="C138" s="1">
+        <v>3846</v>
+      </c>
       <c r="D138" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>308</v>
+      </c>
+      <c r="E138" s="1">
+        <v>88</v>
+      </c>
+      <c r="F138" s="1">
+        <v>5</v>
+      </c>
+      <c r="G138" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="H138" s="1">
+        <v>184</v>
+      </c>
+      <c r="I138" s="1">
+        <v>12</v>
+      </c>
+      <c r="J138" s="1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="1:10">
       <c r="A139" s="2">
         <v>46098</v>
       </c>
+      <c r="B139" s="1">
+        <v>3484</v>
+      </c>
+      <c r="C139" s="1">
+        <v>3241</v>
+      </c>
       <c r="D139" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>243</v>
+      </c>
+      <c r="E139" s="1">
+        <v>86</v>
+      </c>
+      <c r="F139" s="1">
+        <v>6</v>
+      </c>
+      <c r="G139" s="1">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H139" s="1">
+        <v>214</v>
+      </c>
+      <c r="I139" s="1">
+        <v>4</v>
+      </c>
+      <c r="J139" s="1">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="1:10">
       <c r="A140" s="2">
         <v>46099</v>
       </c>
+      <c r="B140" s="1">
+        <v>5363</v>
+      </c>
+      <c r="C140" s="1">
+        <v>5060</v>
+      </c>
       <c r="D140" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>303</v>
+      </c>
+      <c r="E140" s="1">
+        <v>66</v>
+      </c>
+      <c r="F140" s="1">
+        <v>2</v>
+      </c>
+      <c r="G140" s="1">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="H140" s="1">
+        <v>209</v>
+      </c>
+      <c r="I140" s="1">
+        <v>4</v>
+      </c>
+      <c r="J140" s="1">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="1:10">
       <c r="A141" s="2">
         <v>46100</v>
       </c>
+      <c r="B141" s="1">
+        <v>3976</v>
+      </c>
+      <c r="C141" s="1">
+        <v>3727</v>
+      </c>
       <c r="D141" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>249</v>
+      </c>
+      <c r="E141" s="1">
+        <v>112</v>
+      </c>
+      <c r="F141" s="1">
+        <v>7</v>
+      </c>
+      <c r="G141" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="H141" s="1">
+        <v>226</v>
+      </c>
+      <c r="I141" s="1">
+        <v>5</v>
+      </c>
+      <c r="J141" s="1">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="1:10">
       <c r="A142" s="2">
         <v>46101</v>
       </c>
+      <c r="B142" s="1">
+        <v>2871</v>
+      </c>
+      <c r="C142" s="1">
+        <v>2538</v>
+      </c>
       <c r="D142" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>333</v>
+      </c>
+      <c r="E142" s="1">
+        <v>93</v>
+      </c>
+      <c r="F142" s="1">
+        <v>6</v>
+      </c>
+      <c r="G142" s="1">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H142" s="1">
+        <v>230</v>
+      </c>
+      <c r="I142" s="1">
+        <v>10</v>
+      </c>
+      <c r="J142" s="1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="1:10">
       <c r="A143" s="2">
         <v>46102</v>
       </c>
+      <c r="B143" s="1">
+        <v>3482</v>
+      </c>
+      <c r="C143" s="1">
+        <v>3277</v>
+      </c>
       <c r="D143" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>205</v>
+      </c>
+      <c r="E143" s="1">
+        <v>89</v>
+      </c>
+      <c r="F143" s="1">
+        <v>4</v>
+      </c>
+      <c r="G143" s="1">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="H143" s="1">
+        <v>206</v>
+      </c>
+      <c r="I143" s="1">
+        <v>5</v>
+      </c>
+      <c r="J143" s="1">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:10">
       <c r="A144" s="2">
         <v>46103</v>
       </c>
+      <c r="B144" s="1">
+        <v>276</v>
+      </c>
+      <c r="C144" s="1">
+        <v>129</v>
+      </c>
       <c r="D144" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>147</v>
+      </c>
+      <c r="E144" s="1">
+        <v>9</v>
+      </c>
+      <c r="F144" s="1">
+        <v>1</v>
+      </c>
+      <c r="G144" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+      <c r="I144" s="1">
+        <v>0</v>
+      </c>
+      <c r="J144" s="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="1:10">
       <c r="A145" s="2">
         <v>46104</v>
       </c>
+      <c r="B145" s="1">
+        <v>3263</v>
+      </c>
+      <c r="C145" s="1">
+        <v>3045</v>
+      </c>
       <c r="D145" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>218</v>
+      </c>
+      <c r="E145" s="1">
+        <v>105</v>
+      </c>
+      <c r="F145" s="1">
+        <v>8</v>
+      </c>
+      <c r="G145" s="1">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H145" s="1">
+        <v>215</v>
+      </c>
+      <c r="I145" s="1">
+        <v>4</v>
+      </c>
+      <c r="J145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="1:10">
       <c r="A146" s="2">
         <v>46105</v>
       </c>
+      <c r="B146" s="1">
+        <v>2902</v>
+      </c>
+      <c r="C146" s="1">
+        <v>2589</v>
+      </c>
       <c r="D146" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>313</v>
+      </c>
+      <c r="E146" s="1">
+        <v>113</v>
+      </c>
+      <c r="F146" s="1">
+        <v>10</v>
+      </c>
+      <c r="G146" s="1">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="H146" s="1">
+        <v>201</v>
+      </c>
+      <c r="I146" s="1">
+        <v>8</v>
+      </c>
+      <c r="J146" s="1">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="1:10">
       <c r="A147" s="2">
         <v>46106</v>
       </c>
+      <c r="B147" s="1">
+        <v>2984</v>
+      </c>
+      <c r="C147" s="1">
+        <v>2678</v>
+      </c>
       <c r="D147" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>306</v>
+      </c>
+      <c r="E147" s="1">
+        <v>97</v>
+      </c>
+      <c r="F147" s="1">
+        <v>3</v>
+      </c>
+      <c r="G147" s="1">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="H147" s="1">
+        <v>221</v>
+      </c>
+      <c r="I147" s="1">
+        <v>20</v>
+      </c>
+      <c r="J147" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="1:10">
       <c r="A148" s="2">
         <v>46107</v>
       </c>
+      <c r="B148" s="1">
+        <v>3592</v>
+      </c>
+      <c r="C148" s="1">
+        <v>3367</v>
+      </c>
       <c r="D148" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>225</v>
+      </c>
+      <c r="E148" s="1">
+        <v>123</v>
+      </c>
+      <c r="F148" s="1">
+        <v>8</v>
+      </c>
+      <c r="G148" s="1">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H148" s="1">
+        <v>235</v>
+      </c>
+      <c r="I148" s="1">
+        <v>5</v>
+      </c>
+      <c r="J148" s="1">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="1:10">
       <c r="A149" s="2">
         <v>46108</v>
       </c>
+      <c r="B149" s="1">
+        <v>4403</v>
+      </c>
+      <c r="C149" s="1">
+        <v>4072</v>
+      </c>
       <c r="D149" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>331</v>
+      </c>
+      <c r="E149" s="1">
+        <v>131</v>
+      </c>
+      <c r="F149" s="1">
+        <v>8</v>
+      </c>
+      <c r="G149" s="1">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H149" s="1">
+        <v>219</v>
+      </c>
+      <c r="I149" s="1">
+        <v>12</v>
+      </c>
+      <c r="J149" s="1">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="1:10">
       <c r="A150" s="2">
         <v>46109</v>
       </c>
+      <c r="B150" s="1">
+        <v>2515</v>
+      </c>
+      <c r="C150" s="1">
+        <v>2241</v>
+      </c>
       <c r="D150" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>274</v>
+      </c>
+      <c r="E150" s="1">
+        <v>79</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1</v>
+      </c>
+      <c r="G150" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H150" s="1">
+        <v>95</v>
+      </c>
+      <c r="I150" s="1">
+        <v>11</v>
+      </c>
+      <c r="J150" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="1:10">
       <c r="A151" s="2">
         <v>46110</v>
       </c>
+      <c r="B151" s="1">
+        <v>359</v>
+      </c>
+      <c r="C151" s="1">
+        <v>122</v>
+      </c>
       <c r="D151" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>237</v>
+      </c>
+      <c r="E151" s="1">
+        <v>17</v>
+      </c>
+      <c r="F151" s="1">
+        <v>2</v>
+      </c>
+      <c r="G151" s="1">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="H151" s="1">
+        <v>16</v>
+      </c>
+      <c r="I151" s="1">
+        <v>0</v>
+      </c>
+      <c r="J151" s="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="1:10">
       <c r="A152" s="2">
         <v>46111</v>
       </c>
+      <c r="B152" s="1">
+        <v>2595</v>
+      </c>
+      <c r="C152" s="1">
+        <v>23.7</v>
+      </c>
       <c r="D152" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>2571.3</v>
+      </c>
+      <c r="E152" s="1">
+        <v>94</v>
+      </c>
+      <c r="F152" s="1">
+        <v>2</v>
+      </c>
+      <c r="G152" s="1">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="H152" s="1">
+        <v>212</v>
+      </c>
+      <c r="I152" s="1">
+        <v>3</v>
+      </c>
+      <c r="J152" s="1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="1:10">
       <c r="A153" s="2">
         <v>46112</v>
       </c>
+      <c r="B153" s="1">
+        <v>3526</v>
+      </c>
+      <c r="C153" s="1">
+        <v>3218</v>
+      </c>
       <c r="D153" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>308</v>
+      </c>
+      <c r="E153" s="1">
+        <v>110</v>
+      </c>
+      <c r="F153" s="1">
+        <v>1</v>
+      </c>
+      <c r="G153" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H153" s="1">
+        <v>218</v>
+      </c>
+      <c r="I153" s="1">
+        <v>5</v>
+      </c>
+      <c r="J153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="1:10">
       <c r="A154" s="2">
         <v>46113</v>
       </c>
+      <c r="B154" s="1">
+        <v>3190</v>
+      </c>
+      <c r="C154" s="1">
+        <v>2840</v>
+      </c>
       <c r="D154" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>350</v>
+      </c>
+      <c r="E154" s="1">
+        <v>100</v>
+      </c>
+      <c r="F154" s="1">
+        <v>7</v>
+      </c>
+      <c r="G154" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="H154" s="1">
+        <v>213</v>
+      </c>
+      <c r="I154" s="1">
+        <v>6</v>
+      </c>
+      <c r="J154" s="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="1:10">
       <c r="A155" s="2">
         <v>46114</v>
       </c>
+      <c r="B155" s="1">
+        <v>3901</v>
+      </c>
+      <c r="C155" s="1">
+        <v>3644</v>
+      </c>
       <c r="D155" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>257</v>
+      </c>
+      <c r="E155" s="1">
+        <v>120</v>
+      </c>
+      <c r="F155" s="1">
+        <v>6</v>
+      </c>
+      <c r="G155" s="1">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H155" s="1">
+        <v>219</v>
+      </c>
+      <c r="I155" s="1">
+        <v>15</v>
+      </c>
+      <c r="J155" s="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="1:10">
       <c r="A156" s="2">
         <v>46115</v>
       </c>
+      <c r="B156" s="1">
+        <v>3966</v>
+      </c>
+      <c r="C156" s="1">
+        <v>3420</v>
+      </c>
       <c r="D156" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>546</v>
+      </c>
+      <c r="E156" s="1">
+        <v>122</v>
+      </c>
+      <c r="F156" s="1">
+        <v>7</v>
+      </c>
+      <c r="G156" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="H156" s="1">
+        <v>219</v>
+      </c>
+      <c r="I156" s="1">
+        <v>5</v>
+      </c>
+      <c r="J156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="1:10">
       <c r="A157" s="2">
         <v>46116</v>
       </c>
+      <c r="B157" s="1">
+        <v>2879</v>
+      </c>
+      <c r="C157" s="1">
+        <v>2310</v>
+      </c>
       <c r="D157" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>569</v>
+      </c>
+      <c r="E157" s="1">
+        <v>52</v>
+      </c>
+      <c r="F157" s="1">
+        <v>2</v>
+      </c>
+      <c r="G157" s="1">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="H157" s="1">
+        <v>174</v>
+      </c>
+      <c r="I157" s="1">
+        <v>1</v>
+      </c>
+      <c r="J157" s="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="1:10">
       <c r="A158" s="2">
         <v>46117</v>
       </c>
+      <c r="B158" s="1">
+        <v>444</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1</v>
+      </c>
       <c r="D158" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>443</v>
+      </c>
+      <c r="E158" s="1">
+        <v>9</v>
+      </c>
+      <c r="F158" s="1">
+        <v>1</v>
+      </c>
+      <c r="G158" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H158" s="1">
+        <v>0</v>
+      </c>
+      <c r="I158" s="1">
+        <v>0</v>
+      </c>
+      <c r="J158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="1:10">
       <c r="A159" s="2">
         <v>46118</v>
       </c>
+      <c r="B159" s="1">
+        <v>2245</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1758</v>
+      </c>
       <c r="D159" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>487</v>
+      </c>
+      <c r="E159" s="1">
+        <v>51</v>
+      </c>
+      <c r="F159" s="1">
+        <v>1</v>
+      </c>
+      <c r="G159" s="1">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H159" s="1">
+        <v>75</v>
+      </c>
+      <c r="I159" s="1">
+        <v>1</v>
+      </c>
+      <c r="J159" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="1:10">
       <c r="A160" s="2">
         <v>46119</v>
       </c>
+      <c r="B160" s="1">
+        <v>3973</v>
+      </c>
+      <c r="C160" s="1">
+        <v>3401</v>
+      </c>
       <c r="D160" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>572</v>
+      </c>
+      <c r="E160" s="1">
+        <v>95</v>
+      </c>
+      <c r="F160" s="1">
+        <v>7</v>
+      </c>
+      <c r="G160" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="H160" s="1">
+        <v>167</v>
+      </c>
+      <c r="I160" s="1">
+        <v>6</v>
+      </c>
+      <c r="J160" s="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="1:10">
       <c r="A161" s="2">
         <v>46120</v>
       </c>
+      <c r="B161" s="1">
+        <v>3554</v>
+      </c>
+      <c r="C161" s="1">
+        <v>2864</v>
+      </c>
       <c r="D161" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>690</v>
+      </c>
+      <c r="E161" s="1">
+        <v>126</v>
+      </c>
+      <c r="F161" s="1">
+        <v>9</v>
+      </c>
+      <c r="G161" s="1">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="H161" s="1">
+        <v>206</v>
+      </c>
+      <c r="I161" s="1">
+        <v>5</v>
+      </c>
+      <c r="J161" s="1">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="1:10">
       <c r="A162" s="2">
         <v>46121</v>
       </c>
+      <c r="B162" s="1">
+        <v>3269</v>
+      </c>
+      <c r="C162" s="1">
+        <v>2830</v>
+      </c>
       <c r="D162" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>439</v>
+      </c>
+      <c r="E162" s="1">
+        <v>101</v>
+      </c>
+      <c r="F162" s="1">
+        <v>8</v>
+      </c>
+      <c r="G162" s="1">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H162" s="1">
+        <v>216</v>
+      </c>
+      <c r="I162" s="1">
+        <v>5</v>
+      </c>
+      <c r="J162" s="1">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="1:10">
       <c r="A163" s="2">
         <v>46122</v>
       </c>
+      <c r="B163" s="1">
+        <v>3378</v>
+      </c>
+      <c r="C163" s="1">
+        <v>3098</v>
+      </c>
       <c r="D163" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>280</v>
+      </c>
+      <c r="E163" s="1">
+        <v>83</v>
+      </c>
+      <c r="F163" s="1">
+        <v>6</v>
+      </c>
+      <c r="G163" s="1">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H163" s="1">
+        <v>208</v>
+      </c>
+      <c r="I163" s="1">
+        <v>2</v>
+      </c>
+      <c r="J163" s="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="1:10">
       <c r="A164" s="2">
         <v>46123</v>
       </c>
+      <c r="B164" s="1">
+        <v>3107</v>
+      </c>
+      <c r="C164" s="1">
+        <v>2811</v>
+      </c>
       <c r="D164" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>296</v>
+      </c>
+      <c r="E164" s="1">
+        <v>111</v>
+      </c>
+      <c r="F164" s="1">
+        <v>5</v>
+      </c>
+      <c r="G164" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="H164" s="1">
+        <v>208</v>
+      </c>
+      <c r="I164" s="1">
+        <v>13</v>
+      </c>
+      <c r="J164" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="1:10">
       <c r="A165" s="2">
         <v>46124</v>
       </c>
+      <c r="B165" s="1">
+        <v>251</v>
+      </c>
+      <c r="C165" s="1">
+        <v>10</v>
+      </c>
       <c r="D165" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" customHeight="1" spans="1:4">
+        <f t="shared" si="6"/>
+        <v>241</v>
+      </c>
+      <c r="E165" s="1">
+        <v>14</v>
+      </c>
+      <c r="F165" s="1">
+        <v>2</v>
+      </c>
+      <c r="G165" s="1">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="H165" s="1">
+        <v>0</v>
+      </c>
+      <c r="I165" s="1">
+        <v>0</v>
+      </c>
+      <c r="J165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="1:10">
       <c r="A166" s="2">
         <v>46125</v>
       </c>
+      <c r="B166" s="1">
+        <v>3099</v>
+      </c>
+      <c r="C166" s="1">
+        <v>2848</v>
+      </c>
       <c r="D166" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
+        <v>251</v>
+      </c>
+      <c r="E166" s="1">
+        <v>84</v>
+      </c>
+      <c r="F166" s="1">
+        <v>7</v>
+      </c>
+      <c r="G166" s="1">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="H166" s="1">
+        <v>182</v>
+      </c>
+      <c r="I166" s="1">
+        <v>2</v>
+      </c>
+      <c r="J166" s="1">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="1:10">
+      <c r="A167" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B167" s="1">
+        <v>2713</v>
+      </c>
+      <c r="C167" s="1">
+        <v>2268</v>
+      </c>
+      <c r="D167" s="1">
+        <f t="shared" ref="D167:D193" si="8">B167-C167</f>
+        <v>445</v>
+      </c>
+      <c r="E167" s="1">
+        <v>117</v>
+      </c>
+      <c r="F167" s="1">
+        <v>6</v>
+      </c>
+      <c r="G167" s="1">
+        <v>6</v>
+      </c>
+      <c r="H167" s="1">
+        <v>219</v>
+      </c>
+      <c r="I167" s="1">
+        <v>7</v>
+      </c>
+      <c r="J167" s="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="1:10">
+      <c r="A168" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B168" s="1">
+        <v>3845</v>
+      </c>
+      <c r="C168" s="1">
+        <v>3303</v>
+      </c>
+      <c r="D168" s="1">
+        <f t="shared" si="8"/>
+        <v>542</v>
+      </c>
+      <c r="E168" s="1">
+        <v>133</v>
+      </c>
+      <c r="F168" s="1">
+        <v>6</v>
+      </c>
+      <c r="G168" s="1">
+        <v>6</v>
+      </c>
+      <c r="H168" s="1">
+        <v>211</v>
+      </c>
+      <c r="I168" s="1">
+        <v>3</v>
+      </c>
+      <c r="J168" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="1:10">
+      <c r="A169" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B169" s="1">
+        <v>3042</v>
+      </c>
+      <c r="C169" s="1">
+        <v>2782</v>
+      </c>
+      <c r="D169" s="1">
+        <f t="shared" si="8"/>
+        <v>260</v>
+      </c>
+      <c r="E169" s="1">
+        <v>85</v>
+      </c>
+      <c r="F169" s="1">
+        <v>3</v>
+      </c>
+      <c r="G169" s="1">
+        <v>3</v>
+      </c>
+      <c r="H169" s="1">
+        <v>207</v>
+      </c>
+      <c r="I169" s="1">
+        <v>7</v>
+      </c>
+      <c r="J169" s="1">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="1:10">
+      <c r="A170" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B170" s="1">
+        <v>3339</v>
+      </c>
+      <c r="C170" s="1">
+        <v>3061</v>
+      </c>
+      <c r="D170" s="1">
+        <f t="shared" si="8"/>
+        <v>278</v>
+      </c>
+      <c r="E170" s="1">
+        <v>129</v>
+      </c>
+      <c r="F170" s="1">
+        <v>4</v>
+      </c>
+      <c r="G170" s="1">
+        <v>4</v>
+      </c>
+      <c r="H170" s="1">
+        <v>216</v>
+      </c>
+      <c r="I170" s="1">
+        <v>20</v>
+      </c>
+      <c r="J170" s="1">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="1:10">
+      <c r="A171" s="2">
+        <v>46130</v>
+      </c>
+      <c r="B171" s="1">
+        <v>2138</v>
+      </c>
+      <c r="C171" s="1">
+        <v>1898</v>
+      </c>
+      <c r="D171" s="1">
+        <f t="shared" si="8"/>
+        <v>240</v>
+      </c>
+      <c r="E171" s="1">
+        <v>88</v>
+      </c>
+      <c r="F171" s="1">
+        <v>4</v>
+      </c>
+      <c r="G171" s="1">
+        <v>5</v>
+      </c>
+      <c r="H171" s="1">
+        <v>211</v>
+      </c>
+      <c r="I171" s="1">
+        <v>4</v>
+      </c>
+      <c r="J171" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="1:10">
+      <c r="A172" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B172" s="1">
+        <v>903</v>
+      </c>
+      <c r="C172" s="1">
+        <v>698</v>
+      </c>
+      <c r="D172" s="1">
+        <f t="shared" si="8"/>
+        <v>205</v>
+      </c>
+      <c r="E172" s="1">
+        <v>51</v>
+      </c>
+      <c r="F172" s="1">
+        <v>1</v>
+      </c>
+      <c r="G172" s="1">
+        <v>1</v>
+      </c>
+      <c r="H172" s="1">
+        <v>120</v>
+      </c>
+      <c r="I172" s="1">
+        <v>1</v>
+      </c>
+      <c r="J172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="1:10">
+      <c r="A173" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B173" s="1">
+        <v>3428</v>
+      </c>
+      <c r="C173" s="1">
+        <v>3120</v>
+      </c>
+      <c r="D173" s="1">
+        <f t="shared" si="8"/>
+        <v>308</v>
+      </c>
+      <c r="E173" s="1">
+        <v>150</v>
+      </c>
+      <c r="F173" s="1">
+        <v>5</v>
+      </c>
+      <c r="G173" s="1">
+        <v>5</v>
+      </c>
+      <c r="H173" s="1">
+        <v>216</v>
+      </c>
+      <c r="I173" s="1">
+        <v>4</v>
+      </c>
+      <c r="J173" s="1">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="1:10">
+      <c r="A174" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B174" s="1">
+        <v>3029</v>
+      </c>
+      <c r="C174" s="1">
+        <v>2686</v>
+      </c>
+      <c r="D174" s="1">
+        <f t="shared" si="8"/>
+        <v>343</v>
+      </c>
+      <c r="E174" s="1">
+        <v>73</v>
+      </c>
+      <c r="F174" s="1">
+        <v>9</v>
+      </c>
+      <c r="G174" s="1">
+        <v>9</v>
+      </c>
+      <c r="H174" s="1">
+        <v>213</v>
+      </c>
+      <c r="I174" s="1">
+        <v>6</v>
+      </c>
+      <c r="J174" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="1:10">
+      <c r="A175" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B175" s="1">
+        <v>3734</v>
+      </c>
+      <c r="C175" s="1">
+        <v>3196</v>
+      </c>
+      <c r="D175" s="1">
+        <f t="shared" si="8"/>
+        <v>538</v>
+      </c>
+      <c r="E175" s="1">
+        <v>106</v>
+      </c>
+      <c r="F175" s="1">
+        <v>5</v>
+      </c>
+      <c r="G175" s="1">
+        <v>5</v>
+      </c>
+      <c r="H175" s="1">
+        <v>210</v>
+      </c>
+      <c r="I175" s="1">
+        <v>6</v>
+      </c>
+      <c r="J175" s="1">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="1:10">
+      <c r="A176" s="2">
+        <v>46135</v>
+      </c>
+      <c r="B176" s="1">
+        <v>5060</v>
+      </c>
+      <c r="C176" s="1">
+        <v>4613</v>
+      </c>
+      <c r="D176" s="1">
+        <f t="shared" si="8"/>
+        <v>447</v>
+      </c>
+      <c r="E176" s="1">
+        <v>113</v>
+      </c>
+      <c r="F176" s="1">
+        <v>3</v>
+      </c>
+      <c r="G176" s="1">
+        <v>3</v>
+      </c>
+      <c r="H176" s="1">
+        <v>220</v>
+      </c>
+      <c r="I176" s="1">
+        <v>3</v>
+      </c>
+      <c r="J176" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" spans="1:10">
+      <c r="A177" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B177" s="1">
+        <v>3598</v>
+      </c>
+      <c r="C177" s="1">
+        <v>3293</v>
+      </c>
+      <c r="D177" s="1">
+        <f t="shared" si="8"/>
+        <v>305</v>
+      </c>
+      <c r="E177" s="1">
+        <v>81</v>
+      </c>
+      <c r="F177" s="1">
+        <v>6</v>
+      </c>
+      <c r="G177" s="1">
+        <v>7</v>
+      </c>
+      <c r="H177" s="1">
+        <v>215</v>
+      </c>
+      <c r="I177" s="1">
+        <v>5</v>
+      </c>
+      <c r="J177" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" spans="1:10">
+      <c r="A178" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B178" s="1">
+        <v>3158</v>
+      </c>
+      <c r="C178" s="1">
+        <v>2826</v>
+      </c>
+      <c r="D178" s="1">
+        <f t="shared" si="8"/>
+        <v>332</v>
+      </c>
+      <c r="E178" s="1">
+        <v>84</v>
+      </c>
+      <c r="F178" s="1">
+        <v>5</v>
+      </c>
+      <c r="G178" s="1">
+        <v>5</v>
+      </c>
+      <c r="H178" s="1">
+        <v>192</v>
+      </c>
+      <c r="I178" s="1">
+        <v>2</v>
+      </c>
+      <c r="J178" s="1">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" spans="1:10">
+      <c r="A179" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B179" s="1">
+        <v>267</v>
+      </c>
+      <c r="C179" s="1">
+        <v>5</v>
+      </c>
+      <c r="D179" s="1">
+        <f t="shared" si="8"/>
+        <v>262</v>
+      </c>
+      <c r="E179" s="1">
+        <v>7</v>
+      </c>
+      <c r="F179" s="1">
+        <v>0</v>
+      </c>
+      <c r="G179" s="1">
+        <v>0</v>
+      </c>
+      <c r="H179" s="1">
+        <v>0</v>
+      </c>
+      <c r="I179" s="1">
+        <v>0</v>
+      </c>
+      <c r="J179" s="1">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="1:10">
+      <c r="A180" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B180" s="1">
+        <v>2180</v>
+      </c>
+      <c r="C180" s="1">
+        <v>1875</v>
+      </c>
+      <c r="D180" s="1">
+        <f t="shared" si="8"/>
+        <v>305</v>
+      </c>
+      <c r="E180" s="1">
+        <v>81</v>
+      </c>
+      <c r="F180" s="1">
+        <v>8</v>
+      </c>
+      <c r="G180" s="1">
+        <v>9</v>
+      </c>
+      <c r="H180" s="1">
+        <v>204</v>
+      </c>
+      <c r="I180" s="1">
+        <v>8</v>
+      </c>
+      <c r="J180" s="1">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="1:10">
+      <c r="A181" s="2">
+        <v>46140</v>
+      </c>
+      <c r="D181" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J181" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="1:10">
+      <c r="A182" s="2">
+        <v>46141</v>
+      </c>
+      <c r="D182" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J182" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="1:10">
+      <c r="A183" s="2">
+        <v>46142</v>
+      </c>
+      <c r="D183" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="1:10">
+      <c r="A184" s="2">
+        <v>46143</v>
+      </c>
+      <c r="D184" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J184" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="1:10">
+      <c r="A185" s="2">
+        <v>46144</v>
+      </c>
+      <c r="D185" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J185" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="1:10">
+      <c r="A186" s="2">
+        <v>46145</v>
+      </c>
+      <c r="D186" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J186" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="1:10">
+      <c r="A187" s="2">
+        <v>46146</v>
+      </c>
+      <c r="D187" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J187" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="1:10">
+      <c r="A188" s="2">
+        <v>46147</v>
+      </c>
+      <c r="D188" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J188" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="1:10">
+      <c r="A189" s="2">
+        <v>46148</v>
+      </c>
+      <c r="D189" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J189" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="1:10">
+      <c r="A190" s="2">
+        <v>46149</v>
+      </c>
+      <c r="D190" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J190" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" spans="1:10">
+      <c r="A191" s="2">
+        <v>46150</v>
+      </c>
+      <c r="D191" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J191" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" spans="1:10">
+      <c r="A192" s="2">
+        <v>46151</v>
+      </c>
+      <c r="D192" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J192" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" spans="1:10">
+      <c r="A193" s="2">
+        <v>46152</v>
+      </c>
+      <c r="D193" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J193" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" spans="1:10">
+      <c r="A194" s="2">
+        <v>46153</v>
+      </c>
+      <c r="J194" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12375"/>
+    <workbookView windowWidth="14400" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7200,24 +7200,66 @@
       <c r="A181" s="2">
         <v>46140</v>
       </c>
+      <c r="B181" s="1">
+        <v>3600</v>
+      </c>
+      <c r="C181" s="1">
+        <v>3292</v>
+      </c>
       <c r="D181" s="1">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>308</v>
+      </c>
+      <c r="E181" s="1">
+        <v>66</v>
+      </c>
+      <c r="F181" s="1">
+        <v>5</v>
+      </c>
+      <c r="G181" s="1">
+        <v>6</v>
+      </c>
+      <c r="H181" s="1">
+        <v>206</v>
+      </c>
+      <c r="I181" s="1">
+        <v>3</v>
       </c>
       <c r="J181" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:10">
       <c r="A182" s="2">
         <v>46141</v>
       </c>
+      <c r="B182" s="1">
+        <v>2495</v>
+      </c>
+      <c r="C182" s="1">
+        <v>2237</v>
+      </c>
       <c r="D182" s="1">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>258</v>
+      </c>
+      <c r="E182" s="1">
+        <v>59</v>
+      </c>
+      <c r="F182" s="1">
+        <v>3</v>
+      </c>
+      <c r="G182" s="1">
+        <v>4</v>
+      </c>
+      <c r="H182" s="1">
+        <v>214</v>
+      </c>
+      <c r="I182" s="1">
+        <v>1</v>
       </c>
       <c r="J182" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183" customHeight="1" spans="1:10">

--- a/data.xlsx
+++ b/data.xlsx
@@ -7328,19 +7328,33 @@
       <c r="A184" s="3">
         <v>46141</v>
       </c>
+      <c r="B184">
+        <v>5933</v>
+      </c>
+      <c r="C184">
+        <v>5583</v>
+      </c>
       <c r="D184">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>350</v>
+      </c>
+      <c r="E184">
+        <v>126</v>
+      </c>
+      <c r="F184">
+        <v>2</v>
       </c>
       <c r="G184">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H184">
         <v>234</v>
       </c>
       <c r="I184">
         <v>8</v>
+      </c>
+      <c r="J184">
+        <v>309</v>
       </c>
     </row>
     <row r="185" customHeight="1" spans="1:10">
@@ -8518,7 +8532,7 @@
         <v>46272</v>
       </c>
       <c r="G315">
-        <f t="shared" ref="G315:G346" si="14">F315</f>
+        <f t="shared" ref="G315:G352" si="14">F315</f>
         <v>0</v>
       </c>
     </row>
@@ -8806,7 +8820,7 @@
         <v>46304</v>
       </c>
       <c r="G347">
-        <f>F347</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -8815,7 +8829,7 @@
         <v>46305</v>
       </c>
       <c r="G348">
-        <f>F348</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -8824,7 +8838,7 @@
         <v>46306</v>
       </c>
       <c r="G349">
-        <f>F349</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -8833,7 +8847,7 @@
         <v>46307</v>
       </c>
       <c r="G350">
-        <f>F350</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -8842,7 +8856,7 @@
         <v>46308</v>
       </c>
       <c r="G351">
-        <f>F351</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -8851,7 +8865,7 @@
         <v>46309</v>
       </c>
       <c r="G352">
-        <f>F352</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="13545" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6746,7 +6746,7 @@
         <v>2268</v>
       </c>
       <c r="D167" s="1">
-        <f t="shared" ref="D167:D197" si="8">B167-C167</f>
+        <f t="shared" ref="D167:D198" si="8">B167-C167</f>
         <v>445</v>
       </c>
       <c r="E167" s="1">
@@ -7761,6 +7761,34 @@
     <row r="198" customHeight="1" spans="1:10">
       <c r="A198" s="2">
         <v>46157</v>
+      </c>
+      <c r="B198" s="1">
+        <v>4429</v>
+      </c>
+      <c r="C198" s="1">
+        <v>4092</v>
+      </c>
+      <c r="D198" s="1">
+        <f t="shared" si="8"/>
+        <v>337</v>
+      </c>
+      <c r="E198" s="1">
+        <v>67</v>
+      </c>
+      <c r="F198" s="1">
+        <v>11</v>
+      </c>
+      <c r="G198" s="1">
+        <v>12</v>
+      </c>
+      <c r="H198" s="1">
+        <v>228</v>
+      </c>
+      <c r="I198" s="1">
+        <v>6</v>
+      </c>
+      <c r="J198" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="199" customHeight="1" spans="1:10">
